--- a/dym_asia_70記事企画案_殿村.xlsx
+++ b/dym_asia_70記事企画案_殿村.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\との\新しいフォルダー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A88B6B-3988-487E-BCB3-BBAC947D7687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D624336-9C20-4202-A19F-748E6AAF4573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="70記事企画案" sheetId="1" r:id="rId1"/>
@@ -2534,9 +2534,6 @@
     <t>個人事業主 社会保険の具体的な内容・種類</t>
   </si>
   <si>
-    <t>個人事業主 社会保険の種類や特徴を整理します。</t>
-  </si>
-  <si>
     <t>個人事業主 社会保険の実践方法・手順</t>
   </si>
   <si>
@@ -4605,6 +4602,115 @@
   </si>
   <si>
     <t>個人事業主 社会保険に関するよくある疑問Q&amp;A</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/kenkou_iryou/iryouhoken/index.html</t>
+  </si>
+  <si>
+    <t>https://www.smrj.go.jp/kyosai/skyosai/index.html</t>
+  </si>
+  <si>
+    <t>https://laws.e-gov.go.jp/law/333AC0000000192</t>
+  </si>
+  <si>
+    <t>「国民健康保険（国保）」と「健康保険任意継続（任意継続）」の違いを具体的に比較します。特に、国保には「扶養」という概念がなく家族全員分に保険料がかかる一方で、任意継続は会社員時代の扶養制度を最長2年間引き継げる点など、構造的な違いを明示します。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.kyoukaikenpo.or.jp/benefit/voluntary_continuation/</t>
+  </si>
+  <si>
+    <t>https://www.kyoukaikenpo.or.jp/benefit/voluntary_continuation/</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>以下の3つのパターンから、どれを選ぶのが最もコストを抑えられるかの判断基準を提示します。1.所得が低い、または単身の場合: 前年の所得に連動する「国保」が有利になるケースが多い。2.扶養家族が多い場合: 2年間は保険料に上限がある「任意継続」の方が安くなる可能性が高い。3.特定の職種（デザイナー、建設業など）の場合: 定額制の「職域国保組合」が最も安くなる可能性がある。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.bunbi.com/origin.html</t>
+  </si>
+  <si>
+    <t>導入・実施の手順</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>会社員から個人事業主（フリーランス）へ切り替える際の標準的なステップを解説します。1.勤務先での手続き: 社会保険の喪失。2.加入先の選定: 「任意継続」か「国保」かを選択。3.役所・年金事務所での手続き: 窓口または郵送での切り替え。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.nenkin.go.jp/service/kokunen/kanyu/20140710-03.html</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>手続きを一度で済ませるために、必要な持ち物をチェックリスト化します。
+健康保険被保険者資格喪失証明書（退職した会社から発行されるもの）
+本人確認書類（マイナンバーカード、運転免許証など）
+年金手帳または基礎年金番号通知書
+通帳またはクレジットカード（口座振替などを希望する場合）</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>「退職日の翌日から14日以内」という法的期限を強調します。
+即日〜14日: 市区町村役場にて国保・年金の手続き完了。
+2週間〜1ヶ月: 新しい健康保険証が自宅に届く。
+2ヶ月後〜: 保険料の納入通知書が届き、支払いが開始される。
+※期限を過ぎても加入は可能ですが、保険料は退職日まで遡って請求される「遡及加入」になる注意点も伝えます。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://airregi.jp/magazine/guide/3067/#:~:text=%E6%89%8B%E7%B6%9A%E3%81%8D%E3%81%AF%E3%81%8A%E4%BD%8F%E3%81%BE%E3%81%84%E3%81%AE%E5%B8%82,%E6%9B%B8%E9%A1%9E%E3%82%92%E6%8C%81%E5%8F%82%E3%81%97%E3%81%BE%E3%81%99%E3%80%82</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.city.osaka.lg.jp/fukushi/page/0000369739.html#:~:text=%E5%B1%8A%E5%87%BA%E3%81%8C%E9%81%85%E3%82%8C%E3%81%9F%E3%81%A8%E3%81%8D%EF%BC%8814%E6%97%A5%E3%82%92%E9%81%8E%E3%81%8E%E3%81%9F%E3%81%A8%E3%81%8D%EF%BC%89,-%E5%9B%BD%E6%B0%91%E5%81%A5%E5%BA%B7%E4%BF%9D%E9%99%BA&amp;text=%E5%9B%BD%E6%B0%91%E5%81%A5%E5%BA%B7%E4%BF%9D%E9%99%BA%E3%81%AB%E5%8A%A0%E5%85%A5,%E3%81%AB%E3%81%AA%E3%82%8B%E5%A0%B4%E5%90%88%E3%81%8C%E3%81%82%E3%82%8A%E3%81%BE%E3%81%99%E3%80%82</t>
+  </si>
+  <si>
+    <t>最大のメリットは「社会保険料控除」による節税効果です。支払った国民年金・国保料の全額が所得から差し引かれるため、所得税・住民税を直接的に減らせる仕組みを解説します。また、付加年金や国民年金基金を活用することで、将来の受給額を自分の意思で上乗せできる「カスタマイズ性」についても触れます。</t>
+  </si>
+  <si>
+    <t>https://www.nta.go.jp/taxes/shiraberu/taxanswer/shotoku/1130.htm</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>会社員と比較した際の「保障の薄さ」と「負担感」に焦点を当てます。
+傷病手当金・出産手当金がない: 病気やケガで休んでも無収入になるリスク。
+扶養の概念がない: 家族が増えるほど保険料負担がダイレクトに増える点。
+全額自己負担: 会社が半分払ってくれないため、支払額が大きく感じる心理的・経済的負担。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/kenkou_iryou/iryouhoken/index.html</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>「未納の放置」が最も危険であることを伝えます。
+免除・猶予制度の活用: 収入が激減した際は未納にするのではなく、申請を行うことで受給資格期間を守れることを解説。
+遡及払いのリスク: 加入手続きを忘れていても、退職日まで遡って数年分を一括請求される恐れがある点。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>「任意継続」と「国保」、結局どっちが安いですか？
+回答のポイント: 「扶養家族の人数」と「前年の年収」が分かれ道です。年収が高く扶養家族がいるなら、上限額がある「任意継続」が有利になりやすい。逆に単身で所得が下がったなら「国保」の方が安くなる可能性が高いことを伝え、自治体のシミュレーターを勧める。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>所得が少ない場合、保険料は安くなりますか？
+回答のポイント: 「国民健康保険」には所得に応じた7割・5割・2割の「法定軽減制度」があることを解説。ただし、確定申告（または住民税申告）をしていないと適用されないという実務上の注意点を添えます。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>iDeCoや小規模企業共済と社会保険、どちらを優先すべき？
+回答のポイント: まずは義務である社会保険（年金・健康保険）が優先ですが、余裕があれば「小規模企業共済」を検討すべきと回答。これらは社会保険料と同様に「全額所得控除」になるため、セットで考えることで最強の節税＋老後対策になることを伝えます。</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://www.city.shinagawa.tokyo.jp/PC/procedure/procedure-kenkouhoken/procedure-kenkouhoken-hokenryo/hpg000022304.html</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://kyosai-web.smrj.go.jp/skyosai/know/#:~:text=%E5%B0%8F%E8%A6%8F%E6%A8%A1%E4%BC%81%E6%A5%AD%E5%85%B1%E6%B8%88%E3%81%8A%E3%83%88%E3%82%AF%E3%81%AA3%E3%81%A4%E3%81%AE%E3%83%9D%E3%82%A4%E3%83%B3%E3%83%88&amp;text=%E6%BA%80%E6%9C%9F%E3%82%84%E6%BA%80%E9%A1%8D%E3%81%AF%E3%81%82%E3%82%8A%E3%81%BE%E3%81%9B%E3%82%93,%E3%81%A8%E3%81%AA%E3%82%8A%E3%80%81%E7%A8%8E%E5%88%B6%E3%83%A1%E3%83%AA%E3%83%83%E3%83%88%E3%82%82%E3%81%82%E3%82%8A%E3%81%BE%E3%81%99%E3%80%82&amp;text=%E5%A5%91%E7%B4%84%E8%80%85%E3%81%AE%E6%96%B9%E3%81%AF,%E3%82%92%E3%81%94%E5%88%A9%E7%94%A8%E3%81%84%E3%81%9F%E3%81%A0%E3%81%91%E3%81%BE%E3%81%99%E3%80%82</t>
     <phoneticPr fontId="5"/>
   </si>
   <si>
@@ -4633,123 +4739,22 @@
       </rPr>
       <t>「国民年金」を指すことを定義します。 最大の違いは「労使折半（会社が半分負担）」がない点であり、すべての保険料が自己負担になることを明確に伝えます。また、会社員時代の「厚生年金」が「国民年金」に変わることで、将来の受給額が減少するリスクについても触れます。</t>
     </r>
-  </si>
-  <si>
-    <t>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/kenkou_iryou/iryouhoken/index.html</t>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>働き方の多様化（フリーランス・副業の増加）に伴い、会社という盾がない個人が、いかにして病気や老後に備えるかが社会的な課題となっています。 特に、インボイス制度の導入による手取り額の変化や、将来の年金受給額への不安から、「付加年金」や「国民年金基金」「小規模企業共済」といったプラスアルファの制度を活用して自分を守る動きが加速している背景を解説します。</t>
-  </si>
-  <si>
-    <t>https://www.smrj.go.jp/kyosai/skyosai/index.html</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>個人事業主 社会保険の種類や特徴を整理します。</t>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>主に「国民年金法」と「国民健康保険法」に基づいています。 また、近年進んでいる「社会保険の適用拡大」についても触れます。これにより、個人事業主がアルバイトやパートを掛け持ちする場合、その勤務先で社会保険に入れるケースが増えているなど、最新の制度変更を盛り込むと情報の鮮度が上がります。</t>
-  </si>
-  <si>
-    <t>https://laws.e-gov.go.jp/law/333AC0000000192</t>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>個人事業主が関わる社会保険は、大きく分けて「医療保険」「年金保険」「介護保険」の3つに分類されることを解説します。また、会社員とは異なり「雇用保険」や原則として「労災保険」がないことにも触れ、自己責任の範囲が広いことを伝えます。</t>
-  </si>
-  <si>
-    <t>「国民健康保険（国保）」と「健康保険任意継続（任意継続）」の違いを具体的に比較します。特に、国保には「扶養」という概念がなく家族全員分に保険料がかかる一方で、任意継続は会社員時代の扶養制度を最長2年間引き継げる点など、構造的な違いを明示します。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://www.kyoukaikenpo.or.jp/benefit/voluntary_continuation/</t>
-  </si>
-  <si>
-    <t>https://www.kyoukaikenpo.or.jp/benefit/voluntary_continuation/</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>以下の3つのパターンから、どれを選ぶのが最もコストを抑えられるかの判断基準を提示します。1.所得が低い、または単身の場合: 前年の所得に連動する「国保」が有利になるケースが多い。2.扶養家族が多い場合: 2年間は保険料に上限がある「任意継続」の方が安くなる可能性が高い。3.特定の職種（デザイナー、建設業など）の場合: 定額制の「職域国保組合」が最も安くなる可能性がある。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://www.bunbi.com/origin.html</t>
-  </si>
-  <si>
-    <t>導入・実施の手順</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>会社員から個人事業主（フリーランス）へ切り替える際の標準的なステップを解説します。1.勤務先での手続き: 社会保険の喪失。2.加入先の選定: 「任意継続」か「国保」かを選択。3.役所・年金事務所での手続き: 窓口または郵送での切り替え。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://www.nenkin.go.jp/service/kokunen/kanyu/20140710-03.html</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>手続きを一度で済ませるために、必要な持ち物をチェックリスト化します。
-健康保険被保険者資格喪失証明書（退職した会社から発行されるもの）
-本人確認書類（マイナンバーカード、運転免許証など）
-年金手帳または基礎年金番号通知書
-通帳またはクレジットカード（口座振替などを希望する場合）</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>「退職日の翌日から14日以内」という法的期限を強調します。
-即日〜14日: 市区町村役場にて国保・年金の手続き完了。
-2週間〜1ヶ月: 新しい健康保険証が自宅に届く。
-2ヶ月後〜: 保険料の納入通知書が届き、支払いが開始される。
-※期限を過ぎても加入は可能ですが、保険料は退職日まで遡って請求される「遡及加入」になる注意点も伝えます。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://airregi.jp/magazine/guide/3067/#:~:text=%E6%89%8B%E7%B6%9A%E3%81%8D%E3%81%AF%E3%81%8A%E4%BD%8F%E3%81%BE%E3%81%84%E3%81%AE%E5%B8%82,%E6%9B%B8%E9%A1%9E%E3%82%92%E6%8C%81%E5%8F%82%E3%81%97%E3%81%BE%E3%81%99%E3%80%82</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://www.city.osaka.lg.jp/fukushi/page/0000369739.html#:~:text=%E5%B1%8A%E5%87%BA%E3%81%8C%E9%81%85%E3%82%8C%E3%81%9F%E3%81%A8%E3%81%8D%EF%BC%8814%E6%97%A5%E3%82%92%E9%81%8E%E3%81%8E%E3%81%9F%E3%81%A8%E3%81%8D%EF%BC%89,-%E5%9B%BD%E6%B0%91%E5%81%A5%E5%BA%B7%E4%BF%9D%E9%99%BA&amp;text=%E5%9B%BD%E6%B0%91%E5%81%A5%E5%BA%B7%E4%BF%9D%E9%99%BA%E3%81%AB%E5%8A%A0%E5%85%A5,%E3%81%AB%E3%81%AA%E3%82%8B%E5%A0%B4%E5%90%88%E3%81%8C%E3%81%82%E3%82%8A%E3%81%BE%E3%81%99%E3%80%82</t>
-  </si>
-  <si>
-    <t>最大のメリットは「社会保険料控除」による節税効果です。支払った国民年金・国保料の全額が所得から差し引かれるため、所得税・住民税を直接的に減らせる仕組みを解説します。また、付加年金や国民年金基金を活用することで、将来の受給額を自分の意思で上乗せできる「カスタマイズ性」についても触れます。</t>
-  </si>
-  <si>
-    <t>https://www.nta.go.jp/taxes/shiraberu/taxanswer/shotoku/1130.htm</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>会社員と比較した際の「保障の薄さ」と「負担感」に焦点を当てます。
-傷病手当金・出産手当金がない: 病気やケガで休んでも無収入になるリスク。
-扶養の概念がない: 家族が増えるほど保険料負担がダイレクトに増える点。
-全額自己負担: 会社が半分払ってくれないため、支払額が大きく感じる心理的・経済的負担。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/kenkou_iryou/iryouhoken/index.html</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>「未納の放置」が最も危険であることを伝えます。
-免除・猶予制度の活用: 収入が激減した際は未納にするのではなく、申請を行うことで受給資格期間を守れることを解説。
-遡及払いのリスク: 加入手続きを忘れていても、退職日まで遡って数年分を一括請求される恐れがある点。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>「任意継続」と「国保」、結局どっちが安いですか？
-回答のポイント: 「扶養家族の人数」と「前年の年収」が分かれ道です。年収が高く扶養家族がいるなら、上限額がある「任意継続」が有利になりやすい。逆に単身で所得が下がったなら「国保」の方が安くなる可能性が高いことを伝え、自治体のシミュレーターを勧める。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>所得が少ない場合、保険料は安くなりますか？
-回答のポイント: 「国民健康保険」には所得に応じた7割・5割・2割の「法定軽減制度」があることを解説。ただし、確定申告（または住民税申告）をしていないと適用されないという実務上の注意点を添えます。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>iDeCoや小規模企業共済と社会保険、どちらを優先すべき？
-回答のポイント: まずは義務である社会保険（年金・健康保険）が優先ですが、余裕があれば「小規模企業共済」を検討すべきと回答。これらは社会保険料と同様に「全額所得控除」になるため、セットで考えることで最強の節税＋老後対策になることを伝えます。</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://www.city.shinagawa.tokyo.jp/PC/procedure/procedure-kenkouhoken/procedure-kenkouhoken-hokenryo/hpg000022304.html</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>https://kyosai-web.smrj.go.jp/skyosai/know/#:~:text=%E5%B0%8F%E8%A6%8F%E6%A8%A1%E4%BC%81%E6%A5%AD%E5%85%B1%E6%B8%88%E3%81%8A%E3%83%88%E3%82%AF%E3%81%AA3%E3%81%A4%E3%81%AE%E3%83%9D%E3%82%A4%E3%83%B3%E3%83%88&amp;text=%E6%BA%80%E6%9C%9F%E3%82%84%E6%BA%80%E9%A1%8D%E3%81%AF%E3%81%82%E3%82%8A%E3%81%BE%E3%81%9B%E3%82%93,%E3%81%A8%E3%81%AA%E3%82%8A%E3%80%81%E7%A8%8E%E5%88%B6%E3%83%A1%E3%83%AA%E3%83%83%E3%83%88%E3%82%82%E3%81%82%E3%82%8A%E3%81%BE%E3%81%99%E3%80%82&amp;text=%E5%A5%91%E7%B4%84%E8%80%85%E3%81%AE%E6%96%B9%E3%81%AF,%E3%82%92%E3%81%94%E5%88%A9%E7%94%A8%E3%81%84%E3%81%9F%E3%81%A0%E3%81%91%E3%81%BE%E3%81%99%E3%80%82</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -4896,16 +4901,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -5226,18 +5231,18 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
     </row>
     <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -5485,18 +5490,18 @@
       <c r="A26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -5752,18 +5757,18 @@
       <c r="A52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
     </row>
     <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -6011,18 +6016,18 @@
       <c r="A77" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
     </row>
     <row r="78" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
@@ -6270,18 +6275,18 @@
       <c r="A102" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C102" s="5"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
-      <c r="H102" s="5"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="5"/>
-      <c r="K102" s="5"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
     </row>
     <row r="103" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
@@ -6529,18 +6534,18 @@
       <c r="A127" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="5"/>
-      <c r="I127" s="5"/>
-      <c r="J127" s="5"/>
-      <c r="K127" s="5"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="9"/>
+      <c r="H127" s="9"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="9"/>
+      <c r="K127" s="9"/>
     </row>
     <row r="128" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
@@ -6788,18 +6793,18 @@
       <c r="A152" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C152" s="5"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
-      <c r="H152" s="5"/>
-      <c r="I152" s="5"/>
-      <c r="J152" s="5"/>
-      <c r="K152" s="5"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="9"/>
+      <c r="E152" s="9"/>
+      <c r="F152" s="9"/>
+      <c r="G152" s="9"/>
+      <c r="H152" s="9"/>
+      <c r="I152" s="9"/>
+      <c r="J152" s="9"/>
+      <c r="K152" s="9"/>
     </row>
     <row r="153" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
@@ -7055,18 +7060,18 @@
       <c r="A178" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="C178" s="5"/>
-      <c r="D178" s="5"/>
-      <c r="E178" s="5"/>
-      <c r="F178" s="5"/>
-      <c r="G178" s="5"/>
-      <c r="H178" s="5"/>
-      <c r="I178" s="5"/>
-      <c r="J178" s="5"/>
-      <c r="K178" s="5"/>
+      <c r="C178" s="9"/>
+      <c r="D178" s="9"/>
+      <c r="E178" s="9"/>
+      <c r="F178" s="9"/>
+      <c r="G178" s="9"/>
+      <c r="H178" s="9"/>
+      <c r="I178" s="9"/>
+      <c r="J178" s="9"/>
+      <c r="K178" s="9"/>
     </row>
     <row r="179" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
@@ -7314,18 +7319,18 @@
       <c r="A203" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
-      <c r="H203" s="5"/>
-      <c r="I203" s="5"/>
-      <c r="J203" s="5"/>
-      <c r="K203" s="5"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9"/>
+      <c r="G203" s="9"/>
+      <c r="H203" s="9"/>
+      <c r="I203" s="9"/>
+      <c r="J203" s="9"/>
+      <c r="K203" s="9"/>
     </row>
     <row r="204" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
@@ -7573,18 +7578,18 @@
       <c r="A228" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="C228" s="5"/>
-      <c r="D228" s="5"/>
-      <c r="E228" s="5"/>
-      <c r="F228" s="5"/>
-      <c r="G228" s="5"/>
-      <c r="H228" s="5"/>
-      <c r="I228" s="5"/>
-      <c r="J228" s="5"/>
-      <c r="K228" s="5"/>
+      <c r="C228" s="9"/>
+      <c r="D228" s="9"/>
+      <c r="E228" s="9"/>
+      <c r="F228" s="9"/>
+      <c r="G228" s="9"/>
+      <c r="H228" s="9"/>
+      <c r="I228" s="9"/>
+      <c r="J228" s="9"/>
+      <c r="K228" s="9"/>
     </row>
     <row r="229" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
@@ -7840,18 +7845,18 @@
       <c r="A254" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B254" s="4" t="s">
+      <c r="B254" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="C254" s="5"/>
-      <c r="D254" s="5"/>
-      <c r="E254" s="5"/>
-      <c r="F254" s="5"/>
-      <c r="G254" s="5"/>
-      <c r="H254" s="5"/>
-      <c r="I254" s="5"/>
-      <c r="J254" s="5"/>
-      <c r="K254" s="5"/>
+      <c r="C254" s="9"/>
+      <c r="D254" s="9"/>
+      <c r="E254" s="9"/>
+      <c r="F254" s="9"/>
+      <c r="G254" s="9"/>
+      <c r="H254" s="9"/>
+      <c r="I254" s="9"/>
+      <c r="J254" s="9"/>
+      <c r="K254" s="9"/>
     </row>
     <row r="255" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
@@ -8099,18 +8104,18 @@
       <c r="A279" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="C279" s="5"/>
-      <c r="D279" s="5"/>
-      <c r="E279" s="5"/>
-      <c r="F279" s="5"/>
-      <c r="G279" s="5"/>
-      <c r="H279" s="5"/>
-      <c r="I279" s="5"/>
-      <c r="J279" s="5"/>
-      <c r="K279" s="5"/>
+      <c r="C279" s="9"/>
+      <c r="D279" s="9"/>
+      <c r="E279" s="9"/>
+      <c r="F279" s="9"/>
+      <c r="G279" s="9"/>
+      <c r="H279" s="9"/>
+      <c r="I279" s="9"/>
+      <c r="J279" s="9"/>
+      <c r="K279" s="9"/>
     </row>
     <row r="280" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
@@ -8358,18 +8363,18 @@
       <c r="A304" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B304" s="4" t="s">
+      <c r="B304" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C304" s="5"/>
-      <c r="D304" s="5"/>
-      <c r="E304" s="5"/>
-      <c r="F304" s="5"/>
-      <c r="G304" s="5"/>
-      <c r="H304" s="5"/>
-      <c r="I304" s="5"/>
-      <c r="J304" s="5"/>
-      <c r="K304" s="5"/>
+      <c r="C304" s="9"/>
+      <c r="D304" s="9"/>
+      <c r="E304" s="9"/>
+      <c r="F304" s="9"/>
+      <c r="G304" s="9"/>
+      <c r="H304" s="9"/>
+      <c r="I304" s="9"/>
+      <c r="J304" s="9"/>
+      <c r="K304" s="9"/>
     </row>
     <row r="305" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
@@ -8617,18 +8622,18 @@
       <c r="A329" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B329" s="4" t="s">
+      <c r="B329" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="C329" s="5"/>
-      <c r="D329" s="5"/>
-      <c r="E329" s="5"/>
-      <c r="F329" s="5"/>
-      <c r="G329" s="5"/>
-      <c r="H329" s="5"/>
-      <c r="I329" s="5"/>
-      <c r="J329" s="5"/>
-      <c r="K329" s="5"/>
+      <c r="C329" s="9"/>
+      <c r="D329" s="9"/>
+      <c r="E329" s="9"/>
+      <c r="F329" s="9"/>
+      <c r="G329" s="9"/>
+      <c r="H329" s="9"/>
+      <c r="I329" s="9"/>
+      <c r="J329" s="9"/>
+      <c r="K329" s="9"/>
     </row>
     <row r="330" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
@@ -8876,18 +8881,18 @@
       <c r="A354" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="B354" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="C354" s="5"/>
-      <c r="D354" s="5"/>
-      <c r="E354" s="5"/>
-      <c r="F354" s="5"/>
-      <c r="G354" s="5"/>
-      <c r="H354" s="5"/>
-      <c r="I354" s="5"/>
-      <c r="J354" s="5"/>
-      <c r="K354" s="5"/>
+      <c r="C354" s="9"/>
+      <c r="D354" s="9"/>
+      <c r="E354" s="9"/>
+      <c r="F354" s="9"/>
+      <c r="G354" s="9"/>
+      <c r="H354" s="9"/>
+      <c r="I354" s="9"/>
+      <c r="J354" s="9"/>
+      <c r="K354" s="9"/>
     </row>
     <row r="355" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
@@ -9135,18 +9140,18 @@
       <c r="A379" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B379" s="4" t="s">
+      <c r="B379" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="C379" s="5"/>
-      <c r="D379" s="5"/>
-      <c r="E379" s="5"/>
-      <c r="F379" s="5"/>
-      <c r="G379" s="5"/>
-      <c r="H379" s="5"/>
-      <c r="I379" s="5"/>
-      <c r="J379" s="5"/>
-      <c r="K379" s="5"/>
+      <c r="C379" s="9"/>
+      <c r="D379" s="9"/>
+      <c r="E379" s="9"/>
+      <c r="F379" s="9"/>
+      <c r="G379" s="9"/>
+      <c r="H379" s="9"/>
+      <c r="I379" s="9"/>
+      <c r="J379" s="9"/>
+      <c r="K379" s="9"/>
     </row>
     <row r="380" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A380" s="2" t="s">
@@ -9394,18 +9399,18 @@
       <c r="A404" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B404" s="4" t="s">
+      <c r="B404" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="C404" s="5"/>
-      <c r="D404" s="5"/>
-      <c r="E404" s="5"/>
-      <c r="F404" s="5"/>
-      <c r="G404" s="5"/>
-      <c r="H404" s="5"/>
-      <c r="I404" s="5"/>
-      <c r="J404" s="5"/>
-      <c r="K404" s="5"/>
+      <c r="C404" s="9"/>
+      <c r="D404" s="9"/>
+      <c r="E404" s="9"/>
+      <c r="F404" s="9"/>
+      <c r="G404" s="9"/>
+      <c r="H404" s="9"/>
+      <c r="I404" s="9"/>
+      <c r="J404" s="9"/>
+      <c r="K404" s="9"/>
     </row>
     <row r="405" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A405" s="2" t="s">
@@ -9653,18 +9658,18 @@
       <c r="A429" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B429" s="4" t="s">
+      <c r="B429" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="C429" s="5"/>
-      <c r="D429" s="5"/>
-      <c r="E429" s="5"/>
-      <c r="F429" s="5"/>
-      <c r="G429" s="5"/>
-      <c r="H429" s="5"/>
-      <c r="I429" s="5"/>
-      <c r="J429" s="5"/>
-      <c r="K429" s="5"/>
+      <c r="C429" s="9"/>
+      <c r="D429" s="9"/>
+      <c r="E429" s="9"/>
+      <c r="F429" s="9"/>
+      <c r="G429" s="9"/>
+      <c r="H429" s="9"/>
+      <c r="I429" s="9"/>
+      <c r="J429" s="9"/>
+      <c r="K429" s="9"/>
     </row>
     <row r="430" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A430" s="2" t="s">
@@ -9912,18 +9917,18 @@
       <c r="A454" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B454" s="4" t="s">
+      <c r="B454" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="C454" s="5"/>
-      <c r="D454" s="5"/>
-      <c r="E454" s="5"/>
-      <c r="F454" s="5"/>
-      <c r="G454" s="5"/>
-      <c r="H454" s="5"/>
-      <c r="I454" s="5"/>
-      <c r="J454" s="5"/>
-      <c r="K454" s="5"/>
+      <c r="C454" s="9"/>
+      <c r="D454" s="9"/>
+      <c r="E454" s="9"/>
+      <c r="F454" s="9"/>
+      <c r="G454" s="9"/>
+      <c r="H454" s="9"/>
+      <c r="I454" s="9"/>
+      <c r="J454" s="9"/>
+      <c r="K454" s="9"/>
     </row>
     <row r="455" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
@@ -10171,18 +10176,18 @@
       <c r="A479" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B479" s="4" t="s">
+      <c r="B479" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="C479" s="5"/>
-      <c r="D479" s="5"/>
-      <c r="E479" s="5"/>
-      <c r="F479" s="5"/>
-      <c r="G479" s="5"/>
-      <c r="H479" s="5"/>
-      <c r="I479" s="5"/>
-      <c r="J479" s="5"/>
-      <c r="K479" s="5"/>
+      <c r="C479" s="9"/>
+      <c r="D479" s="9"/>
+      <c r="E479" s="9"/>
+      <c r="F479" s="9"/>
+      <c r="G479" s="9"/>
+      <c r="H479" s="9"/>
+      <c r="I479" s="9"/>
+      <c r="J479" s="9"/>
+      <c r="K479" s="9"/>
     </row>
     <row r="480" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A480" s="2" t="s">
@@ -10430,18 +10435,18 @@
       <c r="A504" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B504" s="4" t="s">
+      <c r="B504" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="C504" s="5"/>
-      <c r="D504" s="5"/>
-      <c r="E504" s="5"/>
-      <c r="F504" s="5"/>
-      <c r="G504" s="5"/>
-      <c r="H504" s="5"/>
-      <c r="I504" s="5"/>
-      <c r="J504" s="5"/>
-      <c r="K504" s="5"/>
+      <c r="C504" s="9"/>
+      <c r="D504" s="9"/>
+      <c r="E504" s="9"/>
+      <c r="F504" s="9"/>
+      <c r="G504" s="9"/>
+      <c r="H504" s="9"/>
+      <c r="I504" s="9"/>
+      <c r="J504" s="9"/>
+      <c r="K504" s="9"/>
     </row>
     <row r="505" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A505" s="2" t="s">
@@ -10689,18 +10694,18 @@
       <c r="A529" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B529" s="4" t="s">
+      <c r="B529" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="C529" s="5"/>
-      <c r="D529" s="5"/>
-      <c r="E529" s="5"/>
-      <c r="F529" s="5"/>
-      <c r="G529" s="5"/>
-      <c r="H529" s="5"/>
-      <c r="I529" s="5"/>
-      <c r="J529" s="5"/>
-      <c r="K529" s="5"/>
+      <c r="C529" s="9"/>
+      <c r="D529" s="9"/>
+      <c r="E529" s="9"/>
+      <c r="F529" s="9"/>
+      <c r="G529" s="9"/>
+      <c r="H529" s="9"/>
+      <c r="I529" s="9"/>
+      <c r="J529" s="9"/>
+      <c r="K529" s="9"/>
     </row>
     <row r="530" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
@@ -10948,18 +10953,18 @@
       <c r="A554" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="B554" s="4" t="s">
+      <c r="B554" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="C554" s="5"/>
-      <c r="D554" s="5"/>
-      <c r="E554" s="5"/>
-      <c r="F554" s="5"/>
-      <c r="G554" s="5"/>
-      <c r="H554" s="5"/>
-      <c r="I554" s="5"/>
-      <c r="J554" s="5"/>
-      <c r="K554" s="5"/>
+      <c r="C554" s="9"/>
+      <c r="D554" s="9"/>
+      <c r="E554" s="9"/>
+      <c r="F554" s="9"/>
+      <c r="G554" s="9"/>
+      <c r="H554" s="9"/>
+      <c r="I554" s="9"/>
+      <c r="J554" s="9"/>
+      <c r="K554" s="9"/>
     </row>
     <row r="555" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A555" s="2" t="s">
@@ -11207,18 +11212,18 @@
       <c r="A579" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B579" s="4" t="s">
+      <c r="B579" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="C579" s="5"/>
-      <c r="D579" s="5"/>
-      <c r="E579" s="5"/>
-      <c r="F579" s="5"/>
-      <c r="G579" s="5"/>
-      <c r="H579" s="5"/>
-      <c r="I579" s="5"/>
-      <c r="J579" s="5"/>
-      <c r="K579" s="5"/>
+      <c r="C579" s="9"/>
+      <c r="D579" s="9"/>
+      <c r="E579" s="9"/>
+      <c r="F579" s="9"/>
+      <c r="G579" s="9"/>
+      <c r="H579" s="9"/>
+      <c r="I579" s="9"/>
+      <c r="J579" s="9"/>
+      <c r="K579" s="9"/>
     </row>
     <row r="580" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A580" s="2" t="s">
@@ -11466,18 +11471,18 @@
       <c r="A604" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B604" s="4" t="s">
+      <c r="B604" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="C604" s="5"/>
-      <c r="D604" s="5"/>
-      <c r="E604" s="5"/>
-      <c r="F604" s="5"/>
-      <c r="G604" s="5"/>
-      <c r="H604" s="5"/>
-      <c r="I604" s="5"/>
-      <c r="J604" s="5"/>
-      <c r="K604" s="5"/>
+      <c r="C604" s="9"/>
+      <c r="D604" s="9"/>
+      <c r="E604" s="9"/>
+      <c r="F604" s="9"/>
+      <c r="G604" s="9"/>
+      <c r="H604" s="9"/>
+      <c r="I604" s="9"/>
+      <c r="J604" s="9"/>
+      <c r="K604" s="9"/>
     </row>
     <row r="605" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A605" s="2" t="s">
@@ -11725,18 +11730,18 @@
       <c r="A629" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B629" s="4" t="s">
+      <c r="B629" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="C629" s="5"/>
-      <c r="D629" s="5"/>
-      <c r="E629" s="5"/>
-      <c r="F629" s="5"/>
-      <c r="G629" s="5"/>
-      <c r="H629" s="5"/>
-      <c r="I629" s="5"/>
-      <c r="J629" s="5"/>
-      <c r="K629" s="5"/>
+      <c r="C629" s="9"/>
+      <c r="D629" s="9"/>
+      <c r="E629" s="9"/>
+      <c r="F629" s="9"/>
+      <c r="G629" s="9"/>
+      <c r="H629" s="9"/>
+      <c r="I629" s="9"/>
+      <c r="J629" s="9"/>
+      <c r="K629" s="9"/>
     </row>
     <row r="630" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A630" s="2" t="s">
@@ -11984,18 +11989,18 @@
       <c r="A654" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B654" s="4" t="s">
+      <c r="B654" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C654" s="5"/>
-      <c r="D654" s="5"/>
-      <c r="E654" s="5"/>
-      <c r="F654" s="5"/>
-      <c r="G654" s="5"/>
-      <c r="H654" s="5"/>
-      <c r="I654" s="5"/>
-      <c r="J654" s="5"/>
-      <c r="K654" s="5"/>
+      <c r="C654" s="9"/>
+      <c r="D654" s="9"/>
+      <c r="E654" s="9"/>
+      <c r="F654" s="9"/>
+      <c r="G654" s="9"/>
+      <c r="H654" s="9"/>
+      <c r="I654" s="9"/>
+      <c r="J654" s="9"/>
+      <c r="K654" s="9"/>
     </row>
     <row r="655" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A655" s="2" t="s">
@@ -12243,18 +12248,18 @@
       <c r="A679" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B679" s="4" t="s">
+      <c r="B679" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="C679" s="5"/>
-      <c r="D679" s="5"/>
-      <c r="E679" s="5"/>
-      <c r="F679" s="5"/>
-      <c r="G679" s="5"/>
-      <c r="H679" s="5"/>
-      <c r="I679" s="5"/>
-      <c r="J679" s="5"/>
-      <c r="K679" s="5"/>
+      <c r="C679" s="9"/>
+      <c r="D679" s="9"/>
+      <c r="E679" s="9"/>
+      <c r="F679" s="9"/>
+      <c r="G679" s="9"/>
+      <c r="H679" s="9"/>
+      <c r="I679" s="9"/>
+      <c r="J679" s="9"/>
+      <c r="K679" s="9"/>
     </row>
     <row r="680" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A680" s="2" t="s">
@@ -12502,18 +12507,18 @@
       <c r="A704" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B704" s="4" t="s">
+      <c r="B704" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="C704" s="5"/>
-      <c r="D704" s="5"/>
-      <c r="E704" s="5"/>
-      <c r="F704" s="5"/>
-      <c r="G704" s="5"/>
-      <c r="H704" s="5"/>
-      <c r="I704" s="5"/>
-      <c r="J704" s="5"/>
-      <c r="K704" s="5"/>
+      <c r="C704" s="9"/>
+      <c r="D704" s="9"/>
+      <c r="E704" s="9"/>
+      <c r="F704" s="9"/>
+      <c r="G704" s="9"/>
+      <c r="H704" s="9"/>
+      <c r="I704" s="9"/>
+      <c r="J704" s="9"/>
+      <c r="K704" s="9"/>
     </row>
     <row r="705" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A705" s="2" t="s">
@@ -12761,18 +12766,18 @@
       <c r="A729" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B729" s="4" t="s">
+      <c r="B729" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="C729" s="5"/>
-      <c r="D729" s="5"/>
-      <c r="E729" s="5"/>
-      <c r="F729" s="5"/>
-      <c r="G729" s="5"/>
-      <c r="H729" s="5"/>
-      <c r="I729" s="5"/>
-      <c r="J729" s="5"/>
-      <c r="K729" s="5"/>
+      <c r="C729" s="9"/>
+      <c r="D729" s="9"/>
+      <c r="E729" s="9"/>
+      <c r="F729" s="9"/>
+      <c r="G729" s="9"/>
+      <c r="H729" s="9"/>
+      <c r="I729" s="9"/>
+      <c r="J729" s="9"/>
+      <c r="K729" s="9"/>
     </row>
     <row r="730" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A730" s="2" t="s">
@@ -13020,18 +13025,18 @@
       <c r="A754" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="B754" s="4" t="s">
+      <c r="B754" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="C754" s="5"/>
-      <c r="D754" s="5"/>
-      <c r="E754" s="5"/>
-      <c r="F754" s="5"/>
-      <c r="G754" s="5"/>
-      <c r="H754" s="5"/>
-      <c r="I754" s="5"/>
-      <c r="J754" s="5"/>
-      <c r="K754" s="5"/>
+      <c r="C754" s="9"/>
+      <c r="D754" s="9"/>
+      <c r="E754" s="9"/>
+      <c r="F754" s="9"/>
+      <c r="G754" s="9"/>
+      <c r="H754" s="9"/>
+      <c r="I754" s="9"/>
+      <c r="J754" s="9"/>
+      <c r="K754" s="9"/>
     </row>
     <row r="755" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A755" s="2" t="s">
@@ -13279,18 +13284,18 @@
       <c r="A779" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="B779" s="4" t="s">
+      <c r="B779" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="C779" s="5"/>
-      <c r="D779" s="5"/>
-      <c r="E779" s="5"/>
-      <c r="F779" s="5"/>
-      <c r="G779" s="5"/>
-      <c r="H779" s="5"/>
-      <c r="I779" s="5"/>
-      <c r="J779" s="5"/>
-      <c r="K779" s="5"/>
+      <c r="C779" s="9"/>
+      <c r="D779" s="9"/>
+      <c r="E779" s="9"/>
+      <c r="F779" s="9"/>
+      <c r="G779" s="9"/>
+      <c r="H779" s="9"/>
+      <c r="I779" s="9"/>
+      <c r="J779" s="9"/>
+      <c r="K779" s="9"/>
     </row>
     <row r="780" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A780" s="2" t="s">
@@ -13538,18 +13543,18 @@
       <c r="A804" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="B804" s="4" t="s">
+      <c r="B804" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="C804" s="5"/>
-      <c r="D804" s="5"/>
-      <c r="E804" s="5"/>
-      <c r="F804" s="5"/>
-      <c r="G804" s="5"/>
-      <c r="H804" s="5"/>
-      <c r="I804" s="5"/>
-      <c r="J804" s="5"/>
-      <c r="K804" s="5"/>
+      <c r="C804" s="9"/>
+      <c r="D804" s="9"/>
+      <c r="E804" s="9"/>
+      <c r="F804" s="9"/>
+      <c r="G804" s="9"/>
+      <c r="H804" s="9"/>
+      <c r="I804" s="9"/>
+      <c r="J804" s="9"/>
+      <c r="K804" s="9"/>
     </row>
     <row r="805" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A805" s="2" t="s">
@@ -13797,18 +13802,18 @@
       <c r="A829" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="B829" s="4" t="s">
+      <c r="B829" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="C829" s="5"/>
-      <c r="D829" s="5"/>
-      <c r="E829" s="5"/>
-      <c r="F829" s="5"/>
-      <c r="G829" s="5"/>
-      <c r="H829" s="5"/>
-      <c r="I829" s="5"/>
-      <c r="J829" s="5"/>
-      <c r="K829" s="5"/>
+      <c r="C829" s="9"/>
+      <c r="D829" s="9"/>
+      <c r="E829" s="9"/>
+      <c r="F829" s="9"/>
+      <c r="G829" s="9"/>
+      <c r="H829" s="9"/>
+      <c r="I829" s="9"/>
+      <c r="J829" s="9"/>
+      <c r="K829" s="9"/>
     </row>
     <row r="830" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A830" s="2" t="s">
@@ -13888,10 +13893,10 @@
         <v>824</v>
       </c>
       <c r="F833" t="s">
-        <v>1505</v>
-      </c>
-      <c r="G833" s="8" t="s">
-        <v>1506</v>
+        <v>1529</v>
+      </c>
+      <c r="G833" s="6" t="s">
+        <v>1504</v>
       </c>
     </row>
     <row r="834" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13902,10 +13907,10 @@
         <v>390</v>
       </c>
       <c r="F834" t="s">
-        <v>1507</v>
+        <v>1530</v>
       </c>
       <c r="G834" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="835" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13916,10 +13921,10 @@
         <v>391</v>
       </c>
       <c r="F835" t="s">
-        <v>1509</v>
+        <v>1532</v>
       </c>
       <c r="G835" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="836" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13930,7 +13935,7 @@
         <v>825</v>
       </c>
       <c r="F836" s="3" t="s">
-        <v>826</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="837" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13941,10 +13946,10 @@
         <v>394</v>
       </c>
       <c r="F837" t="s">
-        <v>1511</v>
+        <v>1533</v>
       </c>
       <c r="G837" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="838" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13955,10 +13960,10 @@
         <v>395</v>
       </c>
       <c r="F838" t="s">
-        <v>1512</v>
-      </c>
-      <c r="G838" s="9" t="s">
-        <v>1514</v>
+        <v>1507</v>
+      </c>
+      <c r="G838" s="7" t="s">
+        <v>1509</v>
       </c>
     </row>
     <row r="839" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13969,10 +13974,10 @@
         <v>396</v>
       </c>
       <c r="F839" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="G839" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="840" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13980,10 +13985,10 @@
         <v>38</v>
       </c>
       <c r="D840" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="F840" s="3" t="s">
         <v>827</v>
-      </c>
-      <c r="F840" s="3" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="841" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -13991,13 +13996,13 @@
         <v>41</v>
       </c>
       <c r="E841" s="3" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="F841" t="s">
-        <v>1518</v>
-      </c>
-      <c r="G841" s="9" t="s">
-        <v>1519</v>
+        <v>1513</v>
+      </c>
+      <c r="G841" s="7" t="s">
+        <v>1514</v>
       </c>
     </row>
     <row r="842" spans="2:7" ht="91" x14ac:dyDescent="0.2">
@@ -14007,11 +14012,11 @@
       <c r="E842" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="F842" s="7" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G842" s="9" t="s">
-        <v>1522</v>
+      <c r="F842" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G842" s="7" t="s">
+        <v>1517</v>
       </c>
     </row>
     <row r="843" spans="2:7" ht="78" x14ac:dyDescent="0.2">
@@ -14021,11 +14026,11 @@
       <c r="E843" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="F843" s="7" t="s">
-        <v>1521</v>
+      <c r="F843" s="5" t="s">
+        <v>1516</v>
       </c>
       <c r="G843" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="844" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -14033,10 +14038,10 @@
         <v>47</v>
       </c>
       <c r="D844" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="F844" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="F844" s="3" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="845" spans="2:7" ht="16" x14ac:dyDescent="0.2">
@@ -14047,10 +14052,10 @@
         <v>404</v>
       </c>
       <c r="F845" t="s">
-        <v>1524</v>
-      </c>
-      <c r="G845" s="9" t="s">
-        <v>1525</v>
+        <v>1519</v>
+      </c>
+      <c r="G845" s="7" t="s">
+        <v>1520</v>
       </c>
     </row>
     <row r="846" spans="2:7" ht="91" x14ac:dyDescent="0.2">
@@ -14060,11 +14065,11 @@
       <c r="E846" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F846" s="7" t="s">
-        <v>1526</v>
-      </c>
-      <c r="G846" s="9" t="s">
-        <v>1527</v>
+      <c r="F846" s="5" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G846" s="7" t="s">
+        <v>1522</v>
       </c>
     </row>
     <row r="847" spans="2:7" ht="65" x14ac:dyDescent="0.2">
@@ -14074,8 +14079,8 @@
       <c r="E847" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="F847" s="7" t="s">
-        <v>1528</v>
+      <c r="F847" s="5" t="s">
+        <v>1523</v>
       </c>
       <c r="G847" t="s">
         <v>820</v>
@@ -14085,11 +14090,11 @@
       <c r="B848" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D848" s="6" t="s">
-        <v>1504</v>
+      <c r="D848" s="4" t="s">
+        <v>1503</v>
       </c>
       <c r="F848" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="849" spans="1:11" ht="65" x14ac:dyDescent="0.2">
@@ -14099,11 +14104,11 @@
       <c r="E849" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F849" s="7" t="s">
-        <v>1529</v>
+      <c r="F849" s="5" t="s">
+        <v>1524</v>
       </c>
       <c r="G849" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="850" spans="1:11" ht="52" x14ac:dyDescent="0.2">
@@ -14113,11 +14118,11 @@
       <c r="E850" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="F850" s="7" t="s">
-        <v>1530</v>
-      </c>
-      <c r="G850" s="9" t="s">
-        <v>1532</v>
+      <c r="F850" s="5" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G850" s="7" t="s">
+        <v>1527</v>
       </c>
     </row>
     <row r="851" spans="1:11" ht="65" x14ac:dyDescent="0.2">
@@ -14127,11 +14132,11 @@
       <c r="E851" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="F851" s="7" t="s">
-        <v>1531</v>
+      <c r="F851" s="5" t="s">
+        <v>1526</v>
       </c>
       <c r="G851" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="852" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -14139,25 +14144,25 @@
         <v>65</v>
       </c>
       <c r="F852" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="854" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A854" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B854" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="B854" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="C854" s="5"/>
-      <c r="D854" s="5"/>
-      <c r="E854" s="5"/>
-      <c r="F854" s="5"/>
-      <c r="G854" s="5"/>
-      <c r="H854" s="5"/>
-      <c r="I854" s="5"/>
-      <c r="J854" s="5"/>
-      <c r="K854" s="5"/>
+      <c r="C854" s="9"/>
+      <c r="D854" s="9"/>
+      <c r="E854" s="9"/>
+      <c r="F854" s="9"/>
+      <c r="G854" s="9"/>
+      <c r="H854" s="9"/>
+      <c r="I854" s="9"/>
+      <c r="J854" s="9"/>
+      <c r="K854" s="9"/>
     </row>
     <row r="855" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A855" s="2" t="s">
@@ -14194,28 +14199,28 @@
     </row>
     <row r="856" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A856" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B856" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F856" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="G856" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="G856" s="3" t="s">
+      <c r="H856" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="H856" s="3" t="s">
+      <c r="I856" s="3" t="s">
         <v>838</v>
-      </c>
-      <c r="I856" s="3" t="s">
-        <v>839</v>
       </c>
       <c r="J856" s="3" t="s">
         <v>246</v>
       </c>
       <c r="K856" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="857" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14223,10 +14228,10 @@
         <v>20</v>
       </c>
       <c r="D857" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="F857" s="3" t="s">
         <v>841</v>
-      </c>
-      <c r="F857" s="3" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="858" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14234,7 +14239,7 @@
         <v>23</v>
       </c>
       <c r="E858" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="859" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14258,10 +14263,10 @@
         <v>29</v>
       </c>
       <c r="D861" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="F861" s="3" t="s">
         <v>844</v>
-      </c>
-      <c r="F861" s="3" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="862" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14293,10 +14298,10 @@
         <v>38</v>
       </c>
       <c r="D865" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="F865" s="3" t="s">
         <v>846</v>
-      </c>
-      <c r="F865" s="3" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="866" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14328,10 +14333,10 @@
         <v>47</v>
       </c>
       <c r="D869" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="F869" s="3" t="s">
         <v>848</v>
-      </c>
-      <c r="F869" s="3" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="870" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14363,10 +14368,10 @@
         <v>56</v>
       </c>
       <c r="D873" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="F873" s="3" t="s">
         <v>850</v>
-      </c>
-      <c r="F873" s="3" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="874" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14398,25 +14403,25 @@
         <v>65</v>
       </c>
       <c r="F877" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="879" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A879" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B879" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="B879" s="4" t="s">
-        <v>854</v>
-      </c>
-      <c r="C879" s="5"/>
-      <c r="D879" s="5"/>
-      <c r="E879" s="5"/>
-      <c r="F879" s="5"/>
-      <c r="G879" s="5"/>
-      <c r="H879" s="5"/>
-      <c r="I879" s="5"/>
-      <c r="J879" s="5"/>
-      <c r="K879" s="5"/>
+      <c r="C879" s="9"/>
+      <c r="D879" s="9"/>
+      <c r="E879" s="9"/>
+      <c r="F879" s="9"/>
+      <c r="G879" s="9"/>
+      <c r="H879" s="9"/>
+      <c r="I879" s="9"/>
+      <c r="J879" s="9"/>
+      <c r="K879" s="9"/>
     </row>
     <row r="880" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A880" s="2" t="s">
@@ -14453,13 +14458,13 @@
     </row>
     <row r="881" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A881" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B881" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F881" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G881" s="3" t="s">
         <v>544</v>
@@ -14474,7 +14479,7 @@
         <v>246</v>
       </c>
       <c r="K881" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="882" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14482,10 +14487,10 @@
         <v>20</v>
       </c>
       <c r="D882" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="F882" s="3" t="s">
         <v>858</v>
-      </c>
-      <c r="F882" s="3" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="883" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14493,7 +14498,7 @@
         <v>23</v>
       </c>
       <c r="E883" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="884" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14517,10 +14522,10 @@
         <v>29</v>
       </c>
       <c r="D886" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="F886" s="3" t="s">
         <v>861</v>
-      </c>
-      <c r="F886" s="3" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="887" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14552,10 +14557,10 @@
         <v>38</v>
       </c>
       <c r="D890" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="F890" s="3" t="s">
         <v>863</v>
-      </c>
-      <c r="F890" s="3" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="891" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14587,10 +14592,10 @@
         <v>47</v>
       </c>
       <c r="D894" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="F894" s="3" t="s">
         <v>865</v>
-      </c>
-      <c r="F894" s="3" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="895" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14622,10 +14627,10 @@
         <v>56</v>
       </c>
       <c r="D898" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="F898" s="3" t="s">
         <v>867</v>
-      </c>
-      <c r="F898" s="3" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="899" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14657,25 +14662,25 @@
         <v>65</v>
       </c>
       <c r="F902" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="904" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A904" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B904" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="B904" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="C904" s="5"/>
-      <c r="D904" s="5"/>
-      <c r="E904" s="5"/>
-      <c r="F904" s="5"/>
-      <c r="G904" s="5"/>
-      <c r="H904" s="5"/>
-      <c r="I904" s="5"/>
-      <c r="J904" s="5"/>
-      <c r="K904" s="5"/>
+      <c r="C904" s="9"/>
+      <c r="D904" s="9"/>
+      <c r="E904" s="9"/>
+      <c r="F904" s="9"/>
+      <c r="G904" s="9"/>
+      <c r="H904" s="9"/>
+      <c r="I904" s="9"/>
+      <c r="J904" s="9"/>
+      <c r="K904" s="9"/>
     </row>
     <row r="905" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A905" s="2" t="s">
@@ -14712,13 +14717,13 @@
     </row>
     <row r="906" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A906" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B906" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F906" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G906" s="3" t="s">
         <v>526</v>
@@ -14733,7 +14738,7 @@
         <v>246</v>
       </c>
       <c r="K906" s="3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="907" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14741,10 +14746,10 @@
         <v>20</v>
       </c>
       <c r="D907" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="F907" s="3" t="s">
         <v>875</v>
-      </c>
-      <c r="F907" s="3" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="908" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14752,7 +14757,7 @@
         <v>23</v>
       </c>
       <c r="E908" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="909" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14776,10 +14781,10 @@
         <v>29</v>
       </c>
       <c r="D911" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="F911" s="3" t="s">
         <v>878</v>
-      </c>
-      <c r="F911" s="3" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="912" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -14811,10 +14816,10 @@
         <v>38</v>
       </c>
       <c r="D915" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F915" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="F915" s="3" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="916" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -14846,10 +14851,10 @@
         <v>47</v>
       </c>
       <c r="D919" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="F919" s="3" t="s">
         <v>882</v>
-      </c>
-      <c r="F919" s="3" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="920" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -14881,10 +14886,10 @@
         <v>56</v>
       </c>
       <c r="D923" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F923" s="3" t="s">
         <v>884</v>
-      </c>
-      <c r="F923" s="3" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="924" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -14916,25 +14921,25 @@
         <v>65</v>
       </c>
       <c r="F927" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="929" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A929" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B929" s="8" t="s">
         <v>887</v>
       </c>
-      <c r="B929" s="4" t="s">
-        <v>888</v>
-      </c>
-      <c r="C929" s="5"/>
-      <c r="D929" s="5"/>
-      <c r="E929" s="5"/>
-      <c r="F929" s="5"/>
-      <c r="G929" s="5"/>
-      <c r="H929" s="5"/>
-      <c r="I929" s="5"/>
-      <c r="J929" s="5"/>
-      <c r="K929" s="5"/>
+      <c r="C929" s="9"/>
+      <c r="D929" s="9"/>
+      <c r="E929" s="9"/>
+      <c r="F929" s="9"/>
+      <c r="G929" s="9"/>
+      <c r="H929" s="9"/>
+      <c r="I929" s="9"/>
+      <c r="J929" s="9"/>
+      <c r="K929" s="9"/>
     </row>
     <row r="930" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A930" s="2" t="s">
@@ -14971,13 +14976,13 @@
     </row>
     <row r="931" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A931" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B931" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F931" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G931" s="3" t="s">
         <v>544</v>
@@ -14992,7 +14997,7 @@
         <v>246</v>
       </c>
       <c r="K931" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="932" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15000,10 +15005,10 @@
         <v>20</v>
       </c>
       <c r="D932" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="F932" s="3" t="s">
         <v>892</v>
-      </c>
-      <c r="F932" s="3" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="933" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15011,7 +15016,7 @@
         <v>23</v>
       </c>
       <c r="E933" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="934" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15035,10 +15040,10 @@
         <v>29</v>
       </c>
       <c r="D936" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="F936" s="3" t="s">
         <v>895</v>
-      </c>
-      <c r="F936" s="3" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="937" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15070,10 +15075,10 @@
         <v>38</v>
       </c>
       <c r="D940" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="F940" s="3" t="s">
         <v>897</v>
-      </c>
-      <c r="F940" s="3" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="941" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15105,10 +15110,10 @@
         <v>47</v>
       </c>
       <c r="D944" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="F944" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="F944" s="3" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="945" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15140,10 +15145,10 @@
         <v>56</v>
       </c>
       <c r="D948" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="F948" s="3" t="s">
         <v>901</v>
-      </c>
-      <c r="F948" s="3" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="949" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15175,25 +15180,25 @@
         <v>65</v>
       </c>
       <c r="F952" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="954" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A954" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B954" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="B954" s="4" t="s">
-        <v>905</v>
-      </c>
-      <c r="C954" s="5"/>
-      <c r="D954" s="5"/>
-      <c r="E954" s="5"/>
-      <c r="F954" s="5"/>
-      <c r="G954" s="5"/>
-      <c r="H954" s="5"/>
-      <c r="I954" s="5"/>
-      <c r="J954" s="5"/>
-      <c r="K954" s="5"/>
+      <c r="C954" s="9"/>
+      <c r="D954" s="9"/>
+      <c r="E954" s="9"/>
+      <c r="F954" s="9"/>
+      <c r="G954" s="9"/>
+      <c r="H954" s="9"/>
+      <c r="I954" s="9"/>
+      <c r="J954" s="9"/>
+      <c r="K954" s="9"/>
     </row>
     <row r="955" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A955" s="2" t="s">
@@ -15230,19 +15235,19 @@
     </row>
     <row r="956" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A956" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B956" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F956" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="G956" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="G956" s="3" t="s">
+      <c r="H956" s="3" t="s">
         <v>908</v>
-      </c>
-      <c r="H956" s="3" t="s">
-        <v>909</v>
       </c>
       <c r="I956" s="3" t="s">
         <v>507</v>
@@ -15251,7 +15256,7 @@
         <v>246</v>
       </c>
       <c r="K956" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="957" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15259,10 +15264,10 @@
         <v>20</v>
       </c>
       <c r="D957" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="F957" s="3" t="s">
         <v>911</v>
-      </c>
-      <c r="F957" s="3" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="958" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15270,7 +15275,7 @@
         <v>23</v>
       </c>
       <c r="E958" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="959" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15294,10 +15299,10 @@
         <v>29</v>
       </c>
       <c r="D961" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="F961" s="3" t="s">
         <v>914</v>
-      </c>
-      <c r="F961" s="3" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="962" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15329,10 +15334,10 @@
         <v>38</v>
       </c>
       <c r="D965" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="F965" s="3" t="s">
         <v>916</v>
-      </c>
-      <c r="F965" s="3" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="966" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15364,10 +15369,10 @@
         <v>47</v>
       </c>
       <c r="D969" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="F969" s="3" t="s">
         <v>918</v>
-      </c>
-      <c r="F969" s="3" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="970" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15399,10 +15404,10 @@
         <v>56</v>
       </c>
       <c r="D973" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F973" s="3" t="s">
         <v>920</v>
-      </c>
-      <c r="F973" s="3" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="974" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15434,25 +15439,25 @@
         <v>65</v>
       </c>
       <c r="F977" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="979" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A979" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B979" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="B979" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="C979" s="5"/>
-      <c r="D979" s="5"/>
-      <c r="E979" s="5"/>
-      <c r="F979" s="5"/>
-      <c r="G979" s="5"/>
-      <c r="H979" s="5"/>
-      <c r="I979" s="5"/>
-      <c r="J979" s="5"/>
-      <c r="K979" s="5"/>
+      <c r="C979" s="9"/>
+      <c r="D979" s="9"/>
+      <c r="E979" s="9"/>
+      <c r="F979" s="9"/>
+      <c r="G979" s="9"/>
+      <c r="H979" s="9"/>
+      <c r="I979" s="9"/>
+      <c r="J979" s="9"/>
+      <c r="K979" s="9"/>
     </row>
     <row r="980" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A980" s="2" t="s">
@@ -15489,28 +15494,28 @@
     </row>
     <row r="981" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A981" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B981" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F981" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="G981" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="H981" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="I981" s="3" t="s">
         <v>926</v>
-      </c>
-      <c r="G981" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="H981" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="I981" s="3" t="s">
-        <v>927</v>
       </c>
       <c r="J981" s="3" t="s">
         <v>246</v>
       </c>
       <c r="K981" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="982" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15518,10 +15523,10 @@
         <v>20</v>
       </c>
       <c r="D982" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="F982" s="3" t="s">
         <v>929</v>
-      </c>
-      <c r="F982" s="3" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="983" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15529,7 +15534,7 @@
         <v>23</v>
       </c>
       <c r="E983" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="984" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15553,10 +15558,10 @@
         <v>29</v>
       </c>
       <c r="D986" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="F986" s="3" t="s">
         <v>932</v>
-      </c>
-      <c r="F986" s="3" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="987" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15588,10 +15593,10 @@
         <v>38</v>
       </c>
       <c r="D990" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="F990" s="3" t="s">
         <v>934</v>
-      </c>
-      <c r="F990" s="3" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="991" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15623,10 +15628,10 @@
         <v>47</v>
       </c>
       <c r="D994" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="F994" s="3" t="s">
         <v>936</v>
-      </c>
-      <c r="F994" s="3" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="995" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15658,10 +15663,10 @@
         <v>56</v>
       </c>
       <c r="D998" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="F998" s="3" t="s">
         <v>938</v>
-      </c>
-      <c r="F998" s="3" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="999" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15693,25 +15698,25 @@
         <v>65</v>
       </c>
       <c r="F1002" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="1004" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1004" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B1004" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="B1004" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="C1004" s="5"/>
-      <c r="D1004" s="5"/>
-      <c r="E1004" s="5"/>
-      <c r="F1004" s="5"/>
-      <c r="G1004" s="5"/>
-      <c r="H1004" s="5"/>
-      <c r="I1004" s="5"/>
-      <c r="J1004" s="5"/>
-      <c r="K1004" s="5"/>
+      <c r="C1004" s="9"/>
+      <c r="D1004" s="9"/>
+      <c r="E1004" s="9"/>
+      <c r="F1004" s="9"/>
+      <c r="G1004" s="9"/>
+      <c r="H1004" s="9"/>
+      <c r="I1004" s="9"/>
+      <c r="J1004" s="9"/>
+      <c r="K1004" s="9"/>
     </row>
     <row r="1005" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1005" s="2" t="s">
@@ -15748,28 +15753,28 @@
     </row>
     <row r="1006" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1006" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B1006" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1006" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="G1006" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="G1006" s="3" t="s">
+      <c r="H1006" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="H1006" s="3" t="s">
+      <c r="I1006" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="I1006" s="3" t="s">
+      <c r="J1006" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="J1006" s="3" t="s">
+      <c r="K1006" s="3" t="s">
         <v>948</v>
-      </c>
-      <c r="K1006" s="3" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="1007" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15777,10 +15782,10 @@
         <v>20</v>
       </c>
       <c r="D1007" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="F1007" s="3" t="s">
         <v>950</v>
-      </c>
-      <c r="F1007" s="3" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="1008" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -15788,7 +15793,7 @@
         <v>23</v>
       </c>
       <c r="E1008" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="1009" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15812,10 +15817,10 @@
         <v>29</v>
       </c>
       <c r="D1011" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="F1011" s="3" t="s">
         <v>953</v>
-      </c>
-      <c r="F1011" s="3" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="1012" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15847,10 +15852,10 @@
         <v>38</v>
       </c>
       <c r="D1015" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="F1015" s="3" t="s">
         <v>955</v>
-      </c>
-      <c r="F1015" s="3" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="1016" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15882,10 +15887,10 @@
         <v>47</v>
       </c>
       <c r="D1019" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F1019" s="3" t="s">
         <v>957</v>
-      </c>
-      <c r="F1019" s="3" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="1020" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15917,10 +15922,10 @@
         <v>56</v>
       </c>
       <c r="D1023" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F1023" s="3" t="s">
         <v>959</v>
-      </c>
-      <c r="F1023" s="3" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="1024" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -15952,25 +15957,25 @@
         <v>65</v>
       </c>
       <c r="F1027" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1029" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1029" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1029" s="8" t="s">
         <v>962</v>
       </c>
-      <c r="B1029" s="4" t="s">
-        <v>963</v>
-      </c>
-      <c r="C1029" s="5"/>
-      <c r="D1029" s="5"/>
-      <c r="E1029" s="5"/>
-      <c r="F1029" s="5"/>
-      <c r="G1029" s="5"/>
-      <c r="H1029" s="5"/>
-      <c r="I1029" s="5"/>
-      <c r="J1029" s="5"/>
-      <c r="K1029" s="5"/>
+      <c r="C1029" s="9"/>
+      <c r="D1029" s="9"/>
+      <c r="E1029" s="9"/>
+      <c r="F1029" s="9"/>
+      <c r="G1029" s="9"/>
+      <c r="H1029" s="9"/>
+      <c r="I1029" s="9"/>
+      <c r="J1029" s="9"/>
+      <c r="K1029" s="9"/>
     </row>
     <row r="1030" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1030" s="2" t="s">
@@ -16007,28 +16012,28 @@
     </row>
     <row r="1031" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1031" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B1031" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1031" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="G1031" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="H1031" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="I1031" s="3" t="s">
         <v>965</v>
       </c>
-      <c r="G1031" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="H1031" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="I1031" s="3" t="s">
+      <c r="J1031" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1031" s="3" t="s">
         <v>966</v>
-      </c>
-      <c r="J1031" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1031" s="3" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="1032" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16036,10 +16041,10 @@
         <v>20</v>
       </c>
       <c r="D1032" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="F1032" s="3" t="s">
         <v>968</v>
-      </c>
-      <c r="F1032" s="3" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="1033" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16047,7 +16052,7 @@
         <v>23</v>
       </c>
       <c r="E1033" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="1034" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16071,10 +16076,10 @@
         <v>29</v>
       </c>
       <c r="D1036" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="F1036" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="F1036" s="3" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="1037" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16106,10 +16111,10 @@
         <v>38</v>
       </c>
       <c r="D1040" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="F1040" s="3" t="s">
         <v>973</v>
-      </c>
-      <c r="F1040" s="3" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="1041" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16141,10 +16146,10 @@
         <v>47</v>
       </c>
       <c r="D1044" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="F1044" s="3" t="s">
         <v>975</v>
-      </c>
-      <c r="F1044" s="3" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="1045" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16176,10 +16181,10 @@
         <v>56</v>
       </c>
       <c r="D1048" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="F1048" s="3" t="s">
         <v>977</v>
-      </c>
-      <c r="F1048" s="3" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="1049" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16211,25 +16216,25 @@
         <v>65</v>
       </c>
       <c r="F1052" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="1054" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1054" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B1054" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="B1054" s="4" t="s">
-        <v>981</v>
-      </c>
-      <c r="C1054" s="5"/>
-      <c r="D1054" s="5"/>
-      <c r="E1054" s="5"/>
-      <c r="F1054" s="5"/>
-      <c r="G1054" s="5"/>
-      <c r="H1054" s="5"/>
-      <c r="I1054" s="5"/>
-      <c r="J1054" s="5"/>
-      <c r="K1054" s="5"/>
+      <c r="C1054" s="9"/>
+      <c r="D1054" s="9"/>
+      <c r="E1054" s="9"/>
+      <c r="F1054" s="9"/>
+      <c r="G1054" s="9"/>
+      <c r="H1054" s="9"/>
+      <c r="I1054" s="9"/>
+      <c r="J1054" s="9"/>
+      <c r="K1054" s="9"/>
     </row>
     <row r="1055" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1055" s="2" t="s">
@@ -16266,28 +16271,28 @@
     </row>
     <row r="1056" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1056" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B1056" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1056" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="G1056" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="H1056" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="G1056" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="H1056" s="3" t="s">
+      <c r="I1056" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="J1056" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1056" s="3" t="s">
         <v>984</v>
-      </c>
-      <c r="I1056" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="J1056" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1056" s="3" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="1057" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -16295,10 +16300,10 @@
         <v>20</v>
       </c>
       <c r="D1057" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="F1057" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="F1057" s="3" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="1058" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -16306,7 +16311,7 @@
         <v>23</v>
       </c>
       <c r="E1058" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="1059" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -16330,10 +16335,10 @@
         <v>29</v>
       </c>
       <c r="D1061" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="F1061" s="3" t="s">
         <v>989</v>
-      </c>
-      <c r="F1061" s="3" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="1062" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -16365,10 +16370,10 @@
         <v>38</v>
       </c>
       <c r="D1065" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="F1065" s="3" t="s">
         <v>991</v>
-      </c>
-      <c r="F1065" s="3" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="1066" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -16400,10 +16405,10 @@
         <v>47</v>
       </c>
       <c r="D1069" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="F1069" s="3" t="s">
         <v>993</v>
-      </c>
-      <c r="F1069" s="3" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="1070" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -16435,10 +16440,10 @@
         <v>56</v>
       </c>
       <c r="D1073" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="F1073" s="3" t="s">
         <v>995</v>
-      </c>
-      <c r="F1073" s="3" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="1074" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16470,25 +16475,25 @@
         <v>65</v>
       </c>
       <c r="F1077" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="1079" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1079" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1079" s="8" t="s">
         <v>998</v>
       </c>
-      <c r="B1079" s="4" t="s">
-        <v>999</v>
-      </c>
-      <c r="C1079" s="5"/>
-      <c r="D1079" s="5"/>
-      <c r="E1079" s="5"/>
-      <c r="F1079" s="5"/>
-      <c r="G1079" s="5"/>
-      <c r="H1079" s="5"/>
-      <c r="I1079" s="5"/>
-      <c r="J1079" s="5"/>
-      <c r="K1079" s="5"/>
+      <c r="C1079" s="9"/>
+      <c r="D1079" s="9"/>
+      <c r="E1079" s="9"/>
+      <c r="F1079" s="9"/>
+      <c r="G1079" s="9"/>
+      <c r="H1079" s="9"/>
+      <c r="I1079" s="9"/>
+      <c r="J1079" s="9"/>
+      <c r="K1079" s="9"/>
     </row>
     <row r="1080" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1080" s="2" t="s">
@@ -16525,28 +16530,28 @@
     </row>
     <row r="1081" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1081" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1081" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1081" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G1081" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="H1081" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="I1081" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="J1081" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1081" s="3" t="s">
         <v>1001</v>
-      </c>
-      <c r="G1081" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="H1081" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="I1081" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="J1081" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1081" s="3" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="1082" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16554,10 +16559,10 @@
         <v>20</v>
       </c>
       <c r="D1082" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F1082" s="3" t="s">
         <v>1003</v>
-      </c>
-      <c r="F1082" s="3" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="1083" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16565,7 +16570,7 @@
         <v>23</v>
       </c>
       <c r="E1083" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1084" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16589,10 +16594,10 @@
         <v>29</v>
       </c>
       <c r="D1086" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F1086" s="3" t="s">
         <v>1006</v>
-      </c>
-      <c r="F1086" s="3" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="1087" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16624,10 +16629,10 @@
         <v>38</v>
       </c>
       <c r="D1090" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F1090" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F1090" s="3" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="1091" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16659,10 +16664,10 @@
         <v>47</v>
       </c>
       <c r="D1094" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F1094" s="3" t="s">
         <v>1010</v>
-      </c>
-      <c r="F1094" s="3" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="1095" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16694,10 +16699,10 @@
         <v>56</v>
       </c>
       <c r="D1098" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F1098" s="3" t="s">
         <v>1012</v>
-      </c>
-      <c r="F1098" s="3" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="1099" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16729,25 +16734,25 @@
         <v>65</v>
       </c>
       <c r="F1102" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1104" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1104" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B1104" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="B1104" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C1104" s="5"/>
-      <c r="D1104" s="5"/>
-      <c r="E1104" s="5"/>
-      <c r="F1104" s="5"/>
-      <c r="G1104" s="5"/>
-      <c r="H1104" s="5"/>
-      <c r="I1104" s="5"/>
-      <c r="J1104" s="5"/>
-      <c r="K1104" s="5"/>
+      <c r="C1104" s="9"/>
+      <c r="D1104" s="9"/>
+      <c r="E1104" s="9"/>
+      <c r="F1104" s="9"/>
+      <c r="G1104" s="9"/>
+      <c r="H1104" s="9"/>
+      <c r="I1104" s="9"/>
+      <c r="J1104" s="9"/>
+      <c r="K1104" s="9"/>
     </row>
     <row r="1105" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1105" s="2" t="s">
@@ -16784,28 +16789,28 @@
     </row>
     <row r="1106" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1106" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B1106" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1106" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G1106" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="H1106" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="I1106" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="G1106" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="H1106" s="3" t="s">
+      <c r="J1106" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="I1106" s="3" t="s">
+      <c r="K1106" s="3" t="s">
         <v>1019</v>
-      </c>
-      <c r="J1106" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1106" s="3" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="1107" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16813,10 +16818,10 @@
         <v>20</v>
       </c>
       <c r="D1107" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F1107" s="3" t="s">
         <v>1021</v>
-      </c>
-      <c r="F1107" s="3" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="1108" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16824,7 +16829,7 @@
         <v>23</v>
       </c>
       <c r="E1108" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="1109" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16848,10 +16853,10 @@
         <v>29</v>
       </c>
       <c r="D1111" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F1111" s="3" t="s">
         <v>1024</v>
-      </c>
-      <c r="F1111" s="3" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="1112" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16883,10 +16888,10 @@
         <v>38</v>
       </c>
       <c r="D1115" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F1115" s="3" t="s">
         <v>1026</v>
-      </c>
-      <c r="F1115" s="3" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="1116" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16918,10 +16923,10 @@
         <v>47</v>
       </c>
       <c r="D1119" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F1119" s="3" t="s">
         <v>1028</v>
-      </c>
-      <c r="F1119" s="3" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="1120" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16953,10 +16958,10 @@
         <v>56</v>
       </c>
       <c r="D1123" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1123" s="3" t="s">
         <v>1030</v>
-      </c>
-      <c r="F1123" s="3" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="1124" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -16988,25 +16993,25 @@
         <v>65</v>
       </c>
       <c r="F1127" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="1129" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1129" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B1129" s="8" t="s">
         <v>1033</v>
       </c>
-      <c r="B1129" s="4" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C1129" s="5"/>
-      <c r="D1129" s="5"/>
-      <c r="E1129" s="5"/>
-      <c r="F1129" s="5"/>
-      <c r="G1129" s="5"/>
-      <c r="H1129" s="5"/>
-      <c r="I1129" s="5"/>
-      <c r="J1129" s="5"/>
-      <c r="K1129" s="5"/>
+      <c r="C1129" s="9"/>
+      <c r="D1129" s="9"/>
+      <c r="E1129" s="9"/>
+      <c r="F1129" s="9"/>
+      <c r="G1129" s="9"/>
+      <c r="H1129" s="9"/>
+      <c r="I1129" s="9"/>
+      <c r="J1129" s="9"/>
+      <c r="K1129" s="9"/>
     </row>
     <row r="1130" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1130" s="2" t="s">
@@ -17043,28 +17048,28 @@
     </row>
     <row r="1131" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1131" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B1131" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1131" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G1131" s="3" t="s">
         <v>1036</v>
       </c>
-      <c r="G1131" s="3" t="s">
+      <c r="H1131" s="3" t="s">
         <v>1037</v>
       </c>
-      <c r="H1131" s="3" t="s">
+      <c r="I1131" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="I1131" s="3" t="s">
+      <c r="J1131" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1131" s="3" t="s">
         <v>1039</v>
-      </c>
-      <c r="J1131" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1131" s="3" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="1132" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17072,10 +17077,10 @@
         <v>20</v>
       </c>
       <c r="D1132" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F1132" s="3" t="s">
         <v>1041</v>
-      </c>
-      <c r="F1132" s="3" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="1133" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17083,7 +17088,7 @@
         <v>23</v>
       </c>
       <c r="E1133" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1134" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17107,10 +17112,10 @@
         <v>29</v>
       </c>
       <c r="D1136" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F1136" s="3" t="s">
         <v>1044</v>
-      </c>
-      <c r="F1136" s="3" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="1137" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17142,10 +17147,10 @@
         <v>38</v>
       </c>
       <c r="D1140" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F1140" s="3" t="s">
         <v>1046</v>
-      </c>
-      <c r="F1140" s="3" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="1141" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17177,10 +17182,10 @@
         <v>47</v>
       </c>
       <c r="D1144" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F1144" s="3" t="s">
         <v>1048</v>
-      </c>
-      <c r="F1144" s="3" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="1145" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17212,10 +17217,10 @@
         <v>56</v>
       </c>
       <c r="D1148" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F1148" s="3" t="s">
         <v>1050</v>
-      </c>
-      <c r="F1148" s="3" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="1149" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17247,25 +17252,25 @@
         <v>65</v>
       </c>
       <c r="F1152" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="1154" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1154" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B1154" s="8" t="s">
         <v>1053</v>
       </c>
-      <c r="B1154" s="4" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C1154" s="5"/>
-      <c r="D1154" s="5"/>
-      <c r="E1154" s="5"/>
-      <c r="F1154" s="5"/>
-      <c r="G1154" s="5"/>
-      <c r="H1154" s="5"/>
-      <c r="I1154" s="5"/>
-      <c r="J1154" s="5"/>
-      <c r="K1154" s="5"/>
+      <c r="C1154" s="9"/>
+      <c r="D1154" s="9"/>
+      <c r="E1154" s="9"/>
+      <c r="F1154" s="9"/>
+      <c r="G1154" s="9"/>
+      <c r="H1154" s="9"/>
+      <c r="I1154" s="9"/>
+      <c r="J1154" s="9"/>
+      <c r="K1154" s="9"/>
     </row>
     <row r="1155" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1155" s="2" t="s">
@@ -17302,28 +17307,28 @@
     </row>
     <row r="1156" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1156" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B1156" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1156" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G1156" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="H1156" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="I1156" s="3" t="s">
         <v>1056</v>
       </c>
-      <c r="G1156" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="H1156" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="I1156" s="3" t="s">
+      <c r="J1156" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1156" s="3" t="s">
         <v>1057</v>
-      </c>
-      <c r="J1156" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1156" s="3" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="1157" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17331,10 +17336,10 @@
         <v>20</v>
       </c>
       <c r="D1157" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F1157" s="3" t="s">
         <v>1059</v>
-      </c>
-      <c r="F1157" s="3" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="1158" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17342,7 +17347,7 @@
         <v>23</v>
       </c>
       <c r="E1158" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="1159" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17366,10 +17371,10 @@
         <v>29</v>
       </c>
       <c r="D1161" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F1161" s="3" t="s">
         <v>1062</v>
-      </c>
-      <c r="F1161" s="3" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="1162" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17401,10 +17406,10 @@
         <v>38</v>
       </c>
       <c r="D1165" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F1165" s="3" t="s">
         <v>1064</v>
-      </c>
-      <c r="F1165" s="3" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="1166" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17436,10 +17441,10 @@
         <v>47</v>
       </c>
       <c r="D1169" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F1169" s="3" t="s">
         <v>1066</v>
-      </c>
-      <c r="F1169" s="3" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="1170" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17471,10 +17476,10 @@
         <v>56</v>
       </c>
       <c r="D1173" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F1173" s="3" t="s">
         <v>1068</v>
-      </c>
-      <c r="F1173" s="3" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="1174" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17506,25 +17511,25 @@
         <v>65</v>
       </c>
       <c r="F1177" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="1179" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1179" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B1179" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="B1179" s="4" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C1179" s="5"/>
-      <c r="D1179" s="5"/>
-      <c r="E1179" s="5"/>
-      <c r="F1179" s="5"/>
-      <c r="G1179" s="5"/>
-      <c r="H1179" s="5"/>
-      <c r="I1179" s="5"/>
-      <c r="J1179" s="5"/>
-      <c r="K1179" s="5"/>
+      <c r="C1179" s="9"/>
+      <c r="D1179" s="9"/>
+      <c r="E1179" s="9"/>
+      <c r="F1179" s="9"/>
+      <c r="G1179" s="9"/>
+      <c r="H1179" s="9"/>
+      <c r="I1179" s="9"/>
+      <c r="J1179" s="9"/>
+      <c r="K1179" s="9"/>
     </row>
     <row r="1180" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1180" s="2" t="s">
@@ -17561,28 +17566,28 @@
     </row>
     <row r="1181" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1181" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B1181" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1181" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G1181" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="G1181" s="3" t="s">
+      <c r="H1181" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="H1181" s="3" t="s">
+      <c r="I1181" s="3" t="s">
         <v>1076</v>
       </c>
-      <c r="I1181" s="3" t="s">
+      <c r="J1181" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1181" s="3" t="s">
         <v>1077</v>
-      </c>
-      <c r="J1181" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1181" s="3" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="1182" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17590,10 +17595,10 @@
         <v>20</v>
       </c>
       <c r="D1182" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F1182" s="3" t="s">
         <v>1079</v>
-      </c>
-      <c r="F1182" s="3" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="1183" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17601,7 +17606,7 @@
         <v>23</v>
       </c>
       <c r="E1183" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1184" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17625,10 +17630,10 @@
         <v>29</v>
       </c>
       <c r="D1186" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F1186" s="3" t="s">
         <v>1082</v>
-      </c>
-      <c r="F1186" s="3" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="1187" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17660,10 +17665,10 @@
         <v>38</v>
       </c>
       <c r="D1190" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F1190" s="3" t="s">
         <v>1084</v>
-      </c>
-      <c r="F1190" s="3" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="1191" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17695,10 +17700,10 @@
         <v>47</v>
       </c>
       <c r="D1194" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F1194" s="3" t="s">
         <v>1086</v>
-      </c>
-      <c r="F1194" s="3" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="1195" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17730,10 +17735,10 @@
         <v>56</v>
       </c>
       <c r="D1198" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F1198" s="3" t="s">
         <v>1088</v>
-      </c>
-      <c r="F1198" s="3" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="1199" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -17765,25 +17770,25 @@
         <v>65</v>
       </c>
       <c r="F1202" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="1204" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1204" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B1204" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="B1204" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C1204" s="5"/>
-      <c r="D1204" s="5"/>
-      <c r="E1204" s="5"/>
-      <c r="F1204" s="5"/>
-      <c r="G1204" s="5"/>
-      <c r="H1204" s="5"/>
-      <c r="I1204" s="5"/>
-      <c r="J1204" s="5"/>
-      <c r="K1204" s="5"/>
+      <c r="C1204" s="9"/>
+      <c r="D1204" s="9"/>
+      <c r="E1204" s="9"/>
+      <c r="F1204" s="9"/>
+      <c r="G1204" s="9"/>
+      <c r="H1204" s="9"/>
+      <c r="I1204" s="9"/>
+      <c r="J1204" s="9"/>
+      <c r="K1204" s="9"/>
     </row>
     <row r="1205" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1205" s="2" t="s">
@@ -17820,28 +17825,28 @@
     </row>
     <row r="1206" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1206" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B1206" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1206" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G1206" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="H1206" s="3" t="s">
         <v>1094</v>
       </c>
-      <c r="G1206" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="H1206" s="3" t="s">
+      <c r="I1206" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J1206" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1206" s="3" t="s">
         <v>1095</v>
-      </c>
-      <c r="I1206" s="3" t="s">
-        <v>1057</v>
-      </c>
-      <c r="J1206" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1206" s="3" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="1207" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17849,10 +17854,10 @@
         <v>20</v>
       </c>
       <c r="D1207" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F1207" s="3" t="s">
         <v>1097</v>
-      </c>
-      <c r="F1207" s="3" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="1208" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17860,7 +17865,7 @@
         <v>23</v>
       </c>
       <c r="E1208" s="3" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1209" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17884,10 +17889,10 @@
         <v>29</v>
       </c>
       <c r="D1211" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F1211" s="3" t="s">
         <v>1100</v>
-      </c>
-      <c r="F1211" s="3" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="1212" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17919,10 +17924,10 @@
         <v>38</v>
       </c>
       <c r="D1215" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F1215" s="3" t="s">
         <v>1102</v>
-      </c>
-      <c r="F1215" s="3" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="1216" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17954,10 +17959,10 @@
         <v>47</v>
       </c>
       <c r="D1219" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F1219" s="3" t="s">
         <v>1104</v>
-      </c>
-      <c r="F1219" s="3" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="1220" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -17989,10 +17994,10 @@
         <v>56</v>
       </c>
       <c r="D1223" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F1223" s="3" t="s">
         <v>1106</v>
-      </c>
-      <c r="F1223" s="3" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="1224" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18024,25 +18029,25 @@
         <v>65</v>
       </c>
       <c r="F1227" s="3" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="1229" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1229" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B1229" s="8" t="s">
         <v>1109</v>
       </c>
-      <c r="B1229" s="4" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C1229" s="5"/>
-      <c r="D1229" s="5"/>
-      <c r="E1229" s="5"/>
-      <c r="F1229" s="5"/>
-      <c r="G1229" s="5"/>
-      <c r="H1229" s="5"/>
-      <c r="I1229" s="5"/>
-      <c r="J1229" s="5"/>
-      <c r="K1229" s="5"/>
+      <c r="C1229" s="9"/>
+      <c r="D1229" s="9"/>
+      <c r="E1229" s="9"/>
+      <c r="F1229" s="9"/>
+      <c r="G1229" s="9"/>
+      <c r="H1229" s="9"/>
+      <c r="I1229" s="9"/>
+      <c r="J1229" s="9"/>
+      <c r="K1229" s="9"/>
     </row>
     <row r="1230" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1230" s="2" t="s">
@@ -18079,28 +18084,28 @@
     </row>
     <row r="1231" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1231" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B1231" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1231" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G1231" s="3" t="s">
         <v>1112</v>
       </c>
-      <c r="G1231" s="3" t="s">
+      <c r="H1231" s="3" t="s">
         <v>1113</v>
       </c>
-      <c r="H1231" s="3" t="s">
+      <c r="I1231" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="I1231" s="3" t="s">
+      <c r="J1231" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1231" s="3" t="s">
         <v>1115</v>
-      </c>
-      <c r="J1231" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1231" s="3" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="1232" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18108,10 +18113,10 @@
         <v>20</v>
       </c>
       <c r="D1232" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F1232" s="3" t="s">
         <v>1117</v>
-      </c>
-      <c r="F1232" s="3" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="1233" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -18119,7 +18124,7 @@
         <v>23</v>
       </c>
       <c r="E1233" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="1234" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -18143,10 +18148,10 @@
         <v>29</v>
       </c>
       <c r="D1236" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F1236" s="3" t="s">
         <v>1120</v>
-      </c>
-      <c r="F1236" s="3" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="1237" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -18178,10 +18183,10 @@
         <v>38</v>
       </c>
       <c r="D1240" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F1240" s="3" t="s">
         <v>1122</v>
-      </c>
-      <c r="F1240" s="3" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="1241" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -18213,10 +18218,10 @@
         <v>47</v>
       </c>
       <c r="D1244" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F1244" s="3" t="s">
         <v>1124</v>
-      </c>
-      <c r="F1244" s="3" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="1245" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -18248,10 +18253,10 @@
         <v>56</v>
       </c>
       <c r="D1248" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F1248" s="3" t="s">
         <v>1126</v>
-      </c>
-      <c r="F1248" s="3" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="1249" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18283,25 +18288,25 @@
         <v>65</v>
       </c>
       <c r="F1252" s="3" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1254" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1254" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B1254" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="B1254" s="4" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C1254" s="5"/>
-      <c r="D1254" s="5"/>
-      <c r="E1254" s="5"/>
-      <c r="F1254" s="5"/>
-      <c r="G1254" s="5"/>
-      <c r="H1254" s="5"/>
-      <c r="I1254" s="5"/>
-      <c r="J1254" s="5"/>
-      <c r="K1254" s="5"/>
+      <c r="C1254" s="9"/>
+      <c r="D1254" s="9"/>
+      <c r="E1254" s="9"/>
+      <c r="F1254" s="9"/>
+      <c r="G1254" s="9"/>
+      <c r="H1254" s="9"/>
+      <c r="I1254" s="9"/>
+      <c r="J1254" s="9"/>
+      <c r="K1254" s="9"/>
     </row>
     <row r="1255" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1255" s="2" t="s">
@@ -18338,28 +18343,28 @@
     </row>
     <row r="1256" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1256" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1256" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1256" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G1256" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="G1256" s="3" t="s">
+      <c r="H1256" s="3" t="s">
         <v>1133</v>
       </c>
-      <c r="H1256" s="3" t="s">
+      <c r="I1256" s="3" t="s">
         <v>1134</v>
       </c>
-      <c r="I1256" s="3" t="s">
+      <c r="J1256" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1256" s="3" t="s">
         <v>1135</v>
-      </c>
-      <c r="J1256" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1256" s="3" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="1257" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18367,10 +18372,10 @@
         <v>20</v>
       </c>
       <c r="D1257" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F1257" s="3" t="s">
         <v>1137</v>
-      </c>
-      <c r="F1257" s="3" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="1258" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18378,7 +18383,7 @@
         <v>23</v>
       </c>
       <c r="E1258" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1259" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18402,10 +18407,10 @@
         <v>29</v>
       </c>
       <c r="D1261" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F1261" s="3" t="s">
         <v>1140</v>
-      </c>
-      <c r="F1261" s="3" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="1262" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18437,10 +18442,10 @@
         <v>38</v>
       </c>
       <c r="D1265" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F1265" s="3" t="s">
         <v>1142</v>
-      </c>
-      <c r="F1265" s="3" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="1266" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18472,10 +18477,10 @@
         <v>47</v>
       </c>
       <c r="D1269" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F1269" s="3" t="s">
         <v>1144</v>
-      </c>
-      <c r="F1269" s="3" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="1270" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18507,10 +18512,10 @@
         <v>56</v>
       </c>
       <c r="D1273" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F1273" s="3" t="s">
         <v>1146</v>
-      </c>
-      <c r="F1273" s="3" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="1274" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18542,25 +18547,25 @@
         <v>65</v>
       </c>
       <c r="F1277" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1279" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1279" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B1279" s="8" t="s">
         <v>1149</v>
       </c>
-      <c r="B1279" s="4" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C1279" s="5"/>
-      <c r="D1279" s="5"/>
-      <c r="E1279" s="5"/>
-      <c r="F1279" s="5"/>
-      <c r="G1279" s="5"/>
-      <c r="H1279" s="5"/>
-      <c r="I1279" s="5"/>
-      <c r="J1279" s="5"/>
-      <c r="K1279" s="5"/>
+      <c r="C1279" s="9"/>
+      <c r="D1279" s="9"/>
+      <c r="E1279" s="9"/>
+      <c r="F1279" s="9"/>
+      <c r="G1279" s="9"/>
+      <c r="H1279" s="9"/>
+      <c r="I1279" s="9"/>
+      <c r="J1279" s="9"/>
+      <c r="K1279" s="9"/>
     </row>
     <row r="1280" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1280" s="2" t="s">
@@ -18597,28 +18602,28 @@
     </row>
     <row r="1281" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1281" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B1281" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1281" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G1281" s="3" t="s">
         <v>1152</v>
       </c>
-      <c r="G1281" s="3" t="s">
+      <c r="H1281" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I1281" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J1281" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1281" s="3" t="s">
         <v>1153</v>
-      </c>
-      <c r="H1281" s="3" t="s">
-        <v>1076</v>
-      </c>
-      <c r="I1281" s="3" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J1281" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1281" s="3" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="1282" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18626,10 +18631,10 @@
         <v>20</v>
       </c>
       <c r="D1282" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F1282" s="3" t="s">
         <v>1155</v>
-      </c>
-      <c r="F1282" s="3" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="1283" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18637,7 +18642,7 @@
         <v>23</v>
       </c>
       <c r="E1283" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1284" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18661,10 +18666,10 @@
         <v>29</v>
       </c>
       <c r="D1286" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F1286" s="3" t="s">
         <v>1158</v>
-      </c>
-      <c r="F1286" s="3" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="1287" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18696,10 +18701,10 @@
         <v>38</v>
       </c>
       <c r="D1290" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F1290" s="3" t="s">
         <v>1160</v>
-      </c>
-      <c r="F1290" s="3" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="1291" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18731,10 +18736,10 @@
         <v>47</v>
       </c>
       <c r="D1294" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F1294" s="3" t="s">
         <v>1162</v>
-      </c>
-      <c r="F1294" s="3" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="1295" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18766,10 +18771,10 @@
         <v>56</v>
       </c>
       <c r="D1298" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F1298" s="3" t="s">
         <v>1164</v>
-      </c>
-      <c r="F1298" s="3" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="1299" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18801,25 +18806,25 @@
         <v>65</v>
       </c>
       <c r="F1302" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1304" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1304" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B1304" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="B1304" s="4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C1304" s="5"/>
-      <c r="D1304" s="5"/>
-      <c r="E1304" s="5"/>
-      <c r="F1304" s="5"/>
-      <c r="G1304" s="5"/>
-      <c r="H1304" s="5"/>
-      <c r="I1304" s="5"/>
-      <c r="J1304" s="5"/>
-      <c r="K1304" s="5"/>
+      <c r="C1304" s="9"/>
+      <c r="D1304" s="9"/>
+      <c r="E1304" s="9"/>
+      <c r="F1304" s="9"/>
+      <c r="G1304" s="9"/>
+      <c r="H1304" s="9"/>
+      <c r="I1304" s="9"/>
+      <c r="J1304" s="9"/>
+      <c r="K1304" s="9"/>
     </row>
     <row r="1305" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1305" s="2" t="s">
@@ -18856,28 +18861,28 @@
     </row>
     <row r="1306" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1306" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B1306" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1306" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G1306" s="3" t="s">
         <v>1170</v>
       </c>
-      <c r="G1306" s="3" t="s">
+      <c r="H1306" s="3" t="s">
         <v>1171</v>
       </c>
-      <c r="H1306" s="3" t="s">
+      <c r="I1306" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J1306" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1306" s="3" t="s">
         <v>1172</v>
-      </c>
-      <c r="I1306" s="3" t="s">
-        <v>1135</v>
-      </c>
-      <c r="J1306" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1306" s="3" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="1307" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18885,10 +18890,10 @@
         <v>20</v>
       </c>
       <c r="D1307" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F1307" s="3" t="s">
         <v>1174</v>
-      </c>
-      <c r="F1307" s="3" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="1308" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18896,7 +18901,7 @@
         <v>23</v>
       </c>
       <c r="E1308" s="3" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="1309" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18920,10 +18925,10 @@
         <v>29</v>
       </c>
       <c r="D1311" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F1311" s="3" t="s">
         <v>1177</v>
-      </c>
-      <c r="F1311" s="3" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="1312" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -18955,10 +18960,10 @@
         <v>38</v>
       </c>
       <c r="D1315" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F1315" s="3" t="s">
         <v>1179</v>
-      </c>
-      <c r="F1315" s="3" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="1316" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -18990,10 +18995,10 @@
         <v>47</v>
       </c>
       <c r="D1319" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F1319" s="3" t="s">
         <v>1181</v>
-      </c>
-      <c r="F1319" s="3" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="1320" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19025,10 +19030,10 @@
         <v>56</v>
       </c>
       <c r="D1323" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F1323" s="3" t="s">
         <v>1183</v>
-      </c>
-      <c r="F1323" s="3" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="1324" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19060,25 +19065,25 @@
         <v>65</v>
       </c>
       <c r="F1327" s="3" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="1329" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1329" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1329" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="B1329" s="4" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C1329" s="5"/>
-      <c r="D1329" s="5"/>
-      <c r="E1329" s="5"/>
-      <c r="F1329" s="5"/>
-      <c r="G1329" s="5"/>
-      <c r="H1329" s="5"/>
-      <c r="I1329" s="5"/>
-      <c r="J1329" s="5"/>
-      <c r="K1329" s="5"/>
+      <c r="C1329" s="9"/>
+      <c r="D1329" s="9"/>
+      <c r="E1329" s="9"/>
+      <c r="F1329" s="9"/>
+      <c r="G1329" s="9"/>
+      <c r="H1329" s="9"/>
+      <c r="I1329" s="9"/>
+      <c r="J1329" s="9"/>
+      <c r="K1329" s="9"/>
     </row>
     <row r="1330" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1330" s="2" t="s">
@@ -19115,28 +19120,28 @@
     </row>
     <row r="1331" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1331" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B1331" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1331" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G1331" s="3" t="s">
         <v>1189</v>
       </c>
-      <c r="G1331" s="3" t="s">
+      <c r="H1331" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I1331" s="3" t="s">
         <v>1190</v>
       </c>
-      <c r="H1331" s="3" t="s">
-        <v>1133</v>
-      </c>
-      <c r="I1331" s="3" t="s">
+      <c r="J1331" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="K1331" s="3" t="s">
         <v>1191</v>
-      </c>
-      <c r="J1331" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="K1331" s="3" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="1332" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19144,10 +19149,10 @@
         <v>20</v>
       </c>
       <c r="D1332" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F1332" s="3" t="s">
         <v>1193</v>
-      </c>
-      <c r="F1332" s="3" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="1333" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19155,7 +19160,7 @@
         <v>23</v>
       </c>
       <c r="E1333" s="3" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="1334" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19179,10 +19184,10 @@
         <v>29</v>
       </c>
       <c r="D1336" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F1336" s="3" t="s">
         <v>1196</v>
-      </c>
-      <c r="F1336" s="3" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="1337" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19214,10 +19219,10 @@
         <v>38</v>
       </c>
       <c r="D1340" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F1340" s="3" t="s">
         <v>1198</v>
-      </c>
-      <c r="F1340" s="3" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="1341" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19249,10 +19254,10 @@
         <v>47</v>
       </c>
       <c r="D1344" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1344" s="3" t="s">
         <v>1200</v>
-      </c>
-      <c r="F1344" s="3" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="1345" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19284,10 +19289,10 @@
         <v>56</v>
       </c>
       <c r="D1348" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F1348" s="3" t="s">
         <v>1202</v>
-      </c>
-      <c r="F1348" s="3" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="1349" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19319,25 +19324,25 @@
         <v>65</v>
       </c>
       <c r="F1352" s="3" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="1354" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1354" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1354" s="8" t="s">
         <v>1205</v>
       </c>
-      <c r="B1354" s="4" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C1354" s="5"/>
-      <c r="D1354" s="5"/>
-      <c r="E1354" s="5"/>
-      <c r="F1354" s="5"/>
-      <c r="G1354" s="5"/>
-      <c r="H1354" s="5"/>
-      <c r="I1354" s="5"/>
-      <c r="J1354" s="5"/>
-      <c r="K1354" s="5"/>
+      <c r="C1354" s="9"/>
+      <c r="D1354" s="9"/>
+      <c r="E1354" s="9"/>
+      <c r="F1354" s="9"/>
+      <c r="G1354" s="9"/>
+      <c r="H1354" s="9"/>
+      <c r="I1354" s="9"/>
+      <c r="J1354" s="9"/>
+      <c r="K1354" s="9"/>
     </row>
     <row r="1355" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1355" s="2" t="s">
@@ -19374,28 +19379,28 @@
     </row>
     <row r="1356" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1356" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B1356" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1356" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G1356" s="3" t="s">
         <v>1208</v>
       </c>
-      <c r="G1356" s="3" t="s">
+      <c r="H1356" s="3" t="s">
         <v>1209</v>
       </c>
-      <c r="H1356" s="3" t="s">
+      <c r="I1356" s="3" t="s">
         <v>1210</v>
       </c>
-      <c r="I1356" s="3" t="s">
+      <c r="J1356" s="3" t="s">
         <v>1211</v>
       </c>
-      <c r="J1356" s="3" t="s">
+      <c r="K1356" s="3" t="s">
         <v>1212</v>
-      </c>
-      <c r="K1356" s="3" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="1357" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19403,10 +19408,10 @@
         <v>20</v>
       </c>
       <c r="D1357" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F1357" s="3" t="s">
         <v>1214</v>
-      </c>
-      <c r="F1357" s="3" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="1358" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19414,7 +19419,7 @@
         <v>23</v>
       </c>
       <c r="E1358" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="1359" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19438,10 +19443,10 @@
         <v>29</v>
       </c>
       <c r="D1361" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1361" s="3" t="s">
         <v>1217</v>
-      </c>
-      <c r="F1361" s="3" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="1362" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19473,10 +19478,10 @@
         <v>38</v>
       </c>
       <c r="D1365" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F1365" s="3" t="s">
         <v>1219</v>
-      </c>
-      <c r="F1365" s="3" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="1366" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19508,10 +19513,10 @@
         <v>47</v>
       </c>
       <c r="D1369" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F1369" s="3" t="s">
         <v>1221</v>
-      </c>
-      <c r="F1369" s="3" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="1370" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19543,10 +19548,10 @@
         <v>56</v>
       </c>
       <c r="D1373" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F1373" s="3" t="s">
         <v>1223</v>
-      </c>
-      <c r="F1373" s="3" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="1374" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19578,25 +19583,25 @@
         <v>65</v>
       </c>
       <c r="F1377" s="3" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="1379" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1379" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B1379" s="8" t="s">
         <v>1226</v>
       </c>
-      <c r="B1379" s="4" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C1379" s="5"/>
-      <c r="D1379" s="5"/>
-      <c r="E1379" s="5"/>
-      <c r="F1379" s="5"/>
-      <c r="G1379" s="5"/>
-      <c r="H1379" s="5"/>
-      <c r="I1379" s="5"/>
-      <c r="J1379" s="5"/>
-      <c r="K1379" s="5"/>
+      <c r="C1379" s="9"/>
+      <c r="D1379" s="9"/>
+      <c r="E1379" s="9"/>
+      <c r="F1379" s="9"/>
+      <c r="G1379" s="9"/>
+      <c r="H1379" s="9"/>
+      <c r="I1379" s="9"/>
+      <c r="J1379" s="9"/>
+      <c r="K1379" s="9"/>
     </row>
     <row r="1380" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1380" s="2" t="s">
@@ -19633,28 +19638,28 @@
     </row>
     <row r="1381" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1381" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B1381" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1381" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G1381" s="3" t="s">
         <v>1229</v>
       </c>
-      <c r="G1381" s="3" t="s">
+      <c r="H1381" s="3" t="s">
         <v>1230</v>
       </c>
-      <c r="H1381" s="3" t="s">
+      <c r="I1381" s="3" t="s">
         <v>1231</v>
       </c>
-      <c r="I1381" s="3" t="s">
+      <c r="J1381" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K1381" s="3" t="s">
         <v>1232</v>
-      </c>
-      <c r="J1381" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="K1381" s="3" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="1382" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19662,10 +19667,10 @@
         <v>20</v>
       </c>
       <c r="D1382" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F1382" s="3" t="s">
         <v>1234</v>
-      </c>
-      <c r="F1382" s="3" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="1383" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19673,7 +19678,7 @@
         <v>23</v>
       </c>
       <c r="E1383" s="3" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="1384" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19697,10 +19702,10 @@
         <v>29</v>
       </c>
       <c r="D1386" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F1386" s="3" t="s">
         <v>1237</v>
-      </c>
-      <c r="F1386" s="3" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="1387" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19732,10 +19737,10 @@
         <v>38</v>
       </c>
       <c r="D1390" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F1390" s="3" t="s">
         <v>1239</v>
-      </c>
-      <c r="F1390" s="3" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="1391" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19767,10 +19772,10 @@
         <v>47</v>
       </c>
       <c r="D1394" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F1394" s="3" t="s">
         <v>1241</v>
-      </c>
-      <c r="F1394" s="3" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="1395" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19802,10 +19807,10 @@
         <v>56</v>
       </c>
       <c r="D1398" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F1398" s="3" t="s">
         <v>1243</v>
-      </c>
-      <c r="F1398" s="3" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="1399" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19837,25 +19842,25 @@
         <v>65</v>
       </c>
       <c r="F1402" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="1404" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1404" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B1404" s="8" t="s">
         <v>1246</v>
       </c>
-      <c r="B1404" s="4" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C1404" s="5"/>
-      <c r="D1404" s="5"/>
-      <c r="E1404" s="5"/>
-      <c r="F1404" s="5"/>
-      <c r="G1404" s="5"/>
-      <c r="H1404" s="5"/>
-      <c r="I1404" s="5"/>
-      <c r="J1404" s="5"/>
-      <c r="K1404" s="5"/>
+      <c r="C1404" s="9"/>
+      <c r="D1404" s="9"/>
+      <c r="E1404" s="9"/>
+      <c r="F1404" s="9"/>
+      <c r="G1404" s="9"/>
+      <c r="H1404" s="9"/>
+      <c r="I1404" s="9"/>
+      <c r="J1404" s="9"/>
+      <c r="K1404" s="9"/>
     </row>
     <row r="1405" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1405" s="2" t="s">
@@ -19892,28 +19897,28 @@
     </row>
     <row r="1406" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1406" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B1406" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1406" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1406" s="3" t="s">
         <v>1249</v>
       </c>
-      <c r="G1406" s="3" t="s">
+      <c r="H1406" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="I1406" s="3" t="s">
         <v>1250</v>
       </c>
-      <c r="H1406" s="3" t="s">
-        <v>1210</v>
-      </c>
-      <c r="I1406" s="3" t="s">
+      <c r="J1406" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K1406" s="3" t="s">
         <v>1251</v>
-      </c>
-      <c r="J1406" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="K1406" s="3" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="1407" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19921,10 +19926,10 @@
         <v>20</v>
       </c>
       <c r="D1407" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1407" s="3" t="s">
         <v>1253</v>
-      </c>
-      <c r="F1407" s="3" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="1408" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -19932,7 +19937,7 @@
         <v>23</v>
       </c>
       <c r="E1408" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="1409" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19956,10 +19961,10 @@
         <v>29</v>
       </c>
       <c r="D1411" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F1411" s="3" t="s">
         <v>1256</v>
-      </c>
-      <c r="F1411" s="3" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="1412" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -19991,10 +19996,10 @@
         <v>38</v>
       </c>
       <c r="D1415" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F1415" s="3" t="s">
         <v>1258</v>
-      </c>
-      <c r="F1415" s="3" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="1416" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20026,10 +20031,10 @@
         <v>47</v>
       </c>
       <c r="D1419" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F1419" s="3" t="s">
         <v>1260</v>
-      </c>
-      <c r="F1419" s="3" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="1420" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20061,10 +20066,10 @@
         <v>56</v>
       </c>
       <c r="D1423" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F1423" s="3" t="s">
         <v>1262</v>
-      </c>
-      <c r="F1423" s="3" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="1424" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20096,25 +20101,25 @@
         <v>65</v>
       </c>
       <c r="F1427" s="3" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="1429" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1429" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B1429" s="8" t="s">
         <v>1265</v>
       </c>
-      <c r="B1429" s="4" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C1429" s="5"/>
-      <c r="D1429" s="5"/>
-      <c r="E1429" s="5"/>
-      <c r="F1429" s="5"/>
-      <c r="G1429" s="5"/>
-      <c r="H1429" s="5"/>
-      <c r="I1429" s="5"/>
-      <c r="J1429" s="5"/>
-      <c r="K1429" s="5"/>
+      <c r="C1429" s="9"/>
+      <c r="D1429" s="9"/>
+      <c r="E1429" s="9"/>
+      <c r="F1429" s="9"/>
+      <c r="G1429" s="9"/>
+      <c r="H1429" s="9"/>
+      <c r="I1429" s="9"/>
+      <c r="J1429" s="9"/>
+      <c r="K1429" s="9"/>
     </row>
     <row r="1430" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1430" s="2" t="s">
@@ -20151,28 +20156,28 @@
     </row>
     <row r="1431" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1431" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B1431" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1431" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G1431" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H1431" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I1431" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J1431" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K1431" s="3" t="s">
         <v>1268</v>
-      </c>
-      <c r="G1431" s="3" t="s">
-        <v>1209</v>
-      </c>
-      <c r="H1431" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="I1431" s="3" t="s">
-        <v>1210</v>
-      </c>
-      <c r="J1431" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="K1431" s="3" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="1432" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20180,10 +20185,10 @@
         <v>20</v>
       </c>
       <c r="D1432" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F1432" s="3" t="s">
         <v>1270</v>
-      </c>
-      <c r="F1432" s="3" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="1433" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20191,7 +20196,7 @@
         <v>23</v>
       </c>
       <c r="E1433" s="3" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="1434" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20215,10 +20220,10 @@
         <v>29</v>
       </c>
       <c r="D1436" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F1436" s="3" t="s">
         <v>1273</v>
-      </c>
-      <c r="F1436" s="3" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="1437" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20250,10 +20255,10 @@
         <v>38</v>
       </c>
       <c r="D1440" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F1440" s="3" t="s">
         <v>1275</v>
-      </c>
-      <c r="F1440" s="3" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="1441" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20285,10 +20290,10 @@
         <v>47</v>
       </c>
       <c r="D1444" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F1444" s="3" t="s">
         <v>1277</v>
-      </c>
-      <c r="F1444" s="3" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="1445" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20320,10 +20325,10 @@
         <v>56</v>
       </c>
       <c r="D1448" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F1448" s="3" t="s">
         <v>1279</v>
-      </c>
-      <c r="F1448" s="3" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="1449" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20355,25 +20360,25 @@
         <v>65</v>
       </c>
       <c r="F1452" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1454" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1454" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B1454" s="8" t="s">
         <v>1282</v>
       </c>
-      <c r="B1454" s="4" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C1454" s="5"/>
-      <c r="D1454" s="5"/>
-      <c r="E1454" s="5"/>
-      <c r="F1454" s="5"/>
-      <c r="G1454" s="5"/>
-      <c r="H1454" s="5"/>
-      <c r="I1454" s="5"/>
-      <c r="J1454" s="5"/>
-      <c r="K1454" s="5"/>
+      <c r="C1454" s="9"/>
+      <c r="D1454" s="9"/>
+      <c r="E1454" s="9"/>
+      <c r="F1454" s="9"/>
+      <c r="G1454" s="9"/>
+      <c r="H1454" s="9"/>
+      <c r="I1454" s="9"/>
+      <c r="J1454" s="9"/>
+      <c r="K1454" s="9"/>
     </row>
     <row r="1455" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1455" s="2" t="s">
@@ -20410,28 +20415,28 @@
     </row>
     <row r="1456" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1456" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B1456" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1456" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G1456" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H1456" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I1456" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J1456" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K1456" s="3" t="s">
         <v>1285</v>
-      </c>
-      <c r="G1456" s="3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="H1456" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="I1456" s="3" t="s">
-        <v>1232</v>
-      </c>
-      <c r="J1456" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="K1456" s="3" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="1457" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20439,10 +20444,10 @@
         <v>20</v>
       </c>
       <c r="D1457" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F1457" s="3" t="s">
         <v>1287</v>
-      </c>
-      <c r="F1457" s="3" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="1458" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20450,7 +20455,7 @@
         <v>23</v>
       </c>
       <c r="E1458" s="3" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="1459" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20474,10 +20479,10 @@
         <v>29</v>
       </c>
       <c r="D1461" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F1461" s="3" t="s">
         <v>1290</v>
-      </c>
-      <c r="F1461" s="3" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="1462" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20509,10 +20514,10 @@
         <v>38</v>
       </c>
       <c r="D1465" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F1465" s="3" t="s">
         <v>1292</v>
-      </c>
-      <c r="F1465" s="3" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="1466" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20544,10 +20549,10 @@
         <v>47</v>
       </c>
       <c r="D1469" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F1469" s="3" t="s">
         <v>1294</v>
-      </c>
-      <c r="F1469" s="3" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="1470" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -20579,10 +20584,10 @@
         <v>56</v>
       </c>
       <c r="D1473" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F1473" s="3" t="s">
         <v>1296</v>
-      </c>
-      <c r="F1473" s="3" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="1474" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20614,25 +20619,25 @@
         <v>65</v>
       </c>
       <c r="F1477" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="1479" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1479" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1479" s="8" t="s">
         <v>1299</v>
       </c>
-      <c r="B1479" s="4" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C1479" s="5"/>
-      <c r="D1479" s="5"/>
-      <c r="E1479" s="5"/>
-      <c r="F1479" s="5"/>
-      <c r="G1479" s="5"/>
-      <c r="H1479" s="5"/>
-      <c r="I1479" s="5"/>
-      <c r="J1479" s="5"/>
-      <c r="K1479" s="5"/>
+      <c r="C1479" s="9"/>
+      <c r="D1479" s="9"/>
+      <c r="E1479" s="9"/>
+      <c r="F1479" s="9"/>
+      <c r="G1479" s="9"/>
+      <c r="H1479" s="9"/>
+      <c r="I1479" s="9"/>
+      <c r="J1479" s="9"/>
+      <c r="K1479" s="9"/>
     </row>
     <row r="1480" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1480" s="2" t="s">
@@ -20669,28 +20674,28 @@
     </row>
     <row r="1481" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1481" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B1481" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1481" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G1481" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H1481" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I1481" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J1481" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K1481" s="3" t="s">
         <v>1302</v>
-      </c>
-      <c r="G1481" s="3" t="s">
-        <v>1209</v>
-      </c>
-      <c r="H1481" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="I1481" s="3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="J1481" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="K1481" s="3" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="1482" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20698,10 +20703,10 @@
         <v>20</v>
       </c>
       <c r="D1482" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F1482" s="3" t="s">
         <v>1304</v>
-      </c>
-      <c r="F1482" s="3" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="1483" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20709,7 +20714,7 @@
         <v>23</v>
       </c>
       <c r="E1483" s="3" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="1484" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20733,10 +20738,10 @@
         <v>29</v>
       </c>
       <c r="D1486" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F1486" s="3" t="s">
         <v>1307</v>
-      </c>
-      <c r="F1486" s="3" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="1487" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20768,10 +20773,10 @@
         <v>38</v>
       </c>
       <c r="D1490" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F1490" s="3" t="s">
         <v>1309</v>
-      </c>
-      <c r="F1490" s="3" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="1491" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20803,10 +20808,10 @@
         <v>47</v>
       </c>
       <c r="D1494" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F1494" s="3" t="s">
         <v>1311</v>
-      </c>
-      <c r="F1494" s="3" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="1495" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20838,10 +20843,10 @@
         <v>56</v>
       </c>
       <c r="D1498" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F1498" s="3" t="s">
         <v>1313</v>
-      </c>
-      <c r="F1498" s="3" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="1499" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20873,25 +20878,25 @@
         <v>65</v>
       </c>
       <c r="F1502" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="1504" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1504" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1504" s="8" t="s">
         <v>1316</v>
       </c>
-      <c r="B1504" s="4" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C1504" s="5"/>
-      <c r="D1504" s="5"/>
-      <c r="E1504" s="5"/>
-      <c r="F1504" s="5"/>
-      <c r="G1504" s="5"/>
-      <c r="H1504" s="5"/>
-      <c r="I1504" s="5"/>
-      <c r="J1504" s="5"/>
-      <c r="K1504" s="5"/>
+      <c r="C1504" s="9"/>
+      <c r="D1504" s="9"/>
+      <c r="E1504" s="9"/>
+      <c r="F1504" s="9"/>
+      <c r="G1504" s="9"/>
+      <c r="H1504" s="9"/>
+      <c r="I1504" s="9"/>
+      <c r="J1504" s="9"/>
+      <c r="K1504" s="9"/>
     </row>
     <row r="1505" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1505" s="2" t="s">
@@ -20928,28 +20933,28 @@
     </row>
     <row r="1506" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1506" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B1506" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1506" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G1506" s="3" t="s">
         <v>1319</v>
       </c>
-      <c r="G1506" s="3" t="s">
+      <c r="H1506" s="3" t="s">
         <v>1320</v>
       </c>
-      <c r="H1506" s="3" t="s">
+      <c r="I1506" s="3" t="s">
         <v>1321</v>
       </c>
-      <c r="I1506" s="3" t="s">
+      <c r="J1506" s="3" t="s">
         <v>1322</v>
       </c>
-      <c r="J1506" s="3" t="s">
+      <c r="K1506" s="3" t="s">
         <v>1323</v>
-      </c>
-      <c r="K1506" s="3" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="1507" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20957,10 +20962,10 @@
         <v>20</v>
       </c>
       <c r="D1507" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F1507" s="3" t="s">
         <v>1325</v>
-      </c>
-      <c r="F1507" s="3" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="1508" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20968,7 +20973,7 @@
         <v>23</v>
       </c>
       <c r="E1508" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="1509" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -20992,10 +20997,10 @@
         <v>29</v>
       </c>
       <c r="D1511" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F1511" s="3" t="s">
         <v>1328</v>
-      </c>
-      <c r="F1511" s="3" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="1512" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21027,10 +21032,10 @@
         <v>38</v>
       </c>
       <c r="D1515" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F1515" s="3" t="s">
         <v>1330</v>
-      </c>
-      <c r="F1515" s="3" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="1516" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21062,10 +21067,10 @@
         <v>47</v>
       </c>
       <c r="D1519" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F1519" s="3" t="s">
         <v>1332</v>
-      </c>
-      <c r="F1519" s="3" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="1520" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21097,10 +21102,10 @@
         <v>56</v>
       </c>
       <c r="D1523" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F1523" s="3" t="s">
         <v>1334</v>
-      </c>
-      <c r="F1523" s="3" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="1524" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21132,25 +21137,25 @@
         <v>65</v>
       </c>
       <c r="F1527" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="1529" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1529" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1529" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="B1529" s="4" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C1529" s="5"/>
-      <c r="D1529" s="5"/>
-      <c r="E1529" s="5"/>
-      <c r="F1529" s="5"/>
-      <c r="G1529" s="5"/>
-      <c r="H1529" s="5"/>
-      <c r="I1529" s="5"/>
-      <c r="J1529" s="5"/>
-      <c r="K1529" s="5"/>
+      <c r="C1529" s="9"/>
+      <c r="D1529" s="9"/>
+      <c r="E1529" s="9"/>
+      <c r="F1529" s="9"/>
+      <c r="G1529" s="9"/>
+      <c r="H1529" s="9"/>
+      <c r="I1529" s="9"/>
+      <c r="J1529" s="9"/>
+      <c r="K1529" s="9"/>
     </row>
     <row r="1530" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1530" s="2" t="s">
@@ -21187,28 +21192,28 @@
     </row>
     <row r="1531" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1531" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B1531" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1531" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G1531" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="H1531" s="3" t="s">
         <v>1340</v>
       </c>
-      <c r="G1531" s="3" t="s">
-        <v>1321</v>
-      </c>
-      <c r="H1531" s="3" t="s">
+      <c r="I1531" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J1531" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K1531" s="3" t="s">
         <v>1341</v>
-      </c>
-      <c r="I1531" s="3" t="s">
-        <v>1320</v>
-      </c>
-      <c r="J1531" s="3" t="s">
-        <v>1323</v>
-      </c>
-      <c r="K1531" s="3" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="1532" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21216,10 +21221,10 @@
         <v>20</v>
       </c>
       <c r="D1532" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F1532" s="3" t="s">
         <v>1343</v>
-      </c>
-      <c r="F1532" s="3" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="1533" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21227,7 +21232,7 @@
         <v>23</v>
       </c>
       <c r="E1533" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="1534" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21251,10 +21256,10 @@
         <v>29</v>
       </c>
       <c r="D1536" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F1536" s="3" t="s">
         <v>1346</v>
-      </c>
-      <c r="F1536" s="3" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="1537" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21286,10 +21291,10 @@
         <v>38</v>
       </c>
       <c r="D1540" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F1540" s="3" t="s">
         <v>1348</v>
-      </c>
-      <c r="F1540" s="3" t="s">
-        <v>1349</v>
       </c>
     </row>
     <row r="1541" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21321,10 +21326,10 @@
         <v>47</v>
       </c>
       <c r="D1544" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1544" s="3" t="s">
         <v>1350</v>
-      </c>
-      <c r="F1544" s="3" t="s">
-        <v>1351</v>
       </c>
     </row>
     <row r="1545" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21356,10 +21361,10 @@
         <v>56</v>
       </c>
       <c r="D1548" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F1548" s="3" t="s">
         <v>1352</v>
-      </c>
-      <c r="F1548" s="3" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="1549" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21391,25 +21396,25 @@
         <v>65</v>
       </c>
       <c r="F1552" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="1554" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1554" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1554" s="8" t="s">
         <v>1355</v>
       </c>
-      <c r="B1554" s="4" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C1554" s="5"/>
-      <c r="D1554" s="5"/>
-      <c r="E1554" s="5"/>
-      <c r="F1554" s="5"/>
-      <c r="G1554" s="5"/>
-      <c r="H1554" s="5"/>
-      <c r="I1554" s="5"/>
-      <c r="J1554" s="5"/>
-      <c r="K1554" s="5"/>
+      <c r="C1554" s="9"/>
+      <c r="D1554" s="9"/>
+      <c r="E1554" s="9"/>
+      <c r="F1554" s="9"/>
+      <c r="G1554" s="9"/>
+      <c r="H1554" s="9"/>
+      <c r="I1554" s="9"/>
+      <c r="J1554" s="9"/>
+      <c r="K1554" s="9"/>
     </row>
     <row r="1555" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1555" s="2" t="s">
@@ -21446,28 +21451,28 @@
     </row>
     <row r="1556" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1556" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B1556" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1556" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G1556" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H1556" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I1556" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J1556" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K1556" s="3" t="s">
         <v>1358</v>
-      </c>
-      <c r="G1556" s="3" t="s">
-        <v>1320</v>
-      </c>
-      <c r="H1556" s="3" t="s">
-        <v>1321</v>
-      </c>
-      <c r="I1556" s="3" t="s">
-        <v>1322</v>
-      </c>
-      <c r="J1556" s="3" t="s">
-        <v>1323</v>
-      </c>
-      <c r="K1556" s="3" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="1557" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21475,10 +21480,10 @@
         <v>20</v>
       </c>
       <c r="D1557" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F1557" s="3" t="s">
         <v>1360</v>
-      </c>
-      <c r="F1557" s="3" t="s">
-        <v>1361</v>
       </c>
     </row>
     <row r="1558" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21486,7 +21491,7 @@
         <v>23</v>
       </c>
       <c r="E1558" s="3" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="1559" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21510,10 +21515,10 @@
         <v>29</v>
       </c>
       <c r="D1561" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F1561" s="3" t="s">
         <v>1363</v>
-      </c>
-      <c r="F1561" s="3" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="1562" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21545,10 +21550,10 @@
         <v>38</v>
       </c>
       <c r="D1565" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F1565" s="3" t="s">
         <v>1365</v>
-      </c>
-      <c r="F1565" s="3" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="1566" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21580,10 +21585,10 @@
         <v>47</v>
       </c>
       <c r="D1569" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F1569" s="3" t="s">
         <v>1367</v>
-      </c>
-      <c r="F1569" s="3" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="1570" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21615,10 +21620,10 @@
         <v>56</v>
       </c>
       <c r="D1573" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F1573" s="3" t="s">
         <v>1369</v>
-      </c>
-      <c r="F1573" s="3" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="1574" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21650,25 +21655,25 @@
         <v>65</v>
       </c>
       <c r="F1577" s="3" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="1579" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1579" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B1579" s="8" t="s">
         <v>1372</v>
       </c>
-      <c r="B1579" s="4" t="s">
-        <v>1373</v>
-      </c>
-      <c r="C1579" s="5"/>
-      <c r="D1579" s="5"/>
-      <c r="E1579" s="5"/>
-      <c r="F1579" s="5"/>
-      <c r="G1579" s="5"/>
-      <c r="H1579" s="5"/>
-      <c r="I1579" s="5"/>
-      <c r="J1579" s="5"/>
-      <c r="K1579" s="5"/>
+      <c r="C1579" s="9"/>
+      <c r="D1579" s="9"/>
+      <c r="E1579" s="9"/>
+      <c r="F1579" s="9"/>
+      <c r="G1579" s="9"/>
+      <c r="H1579" s="9"/>
+      <c r="I1579" s="9"/>
+      <c r="J1579" s="9"/>
+      <c r="K1579" s="9"/>
     </row>
     <row r="1580" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1580" s="2" t="s">
@@ -21705,28 +21710,28 @@
     </row>
     <row r="1581" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1581" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B1581" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1581" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G1581" s="3" t="s">
         <v>1375</v>
       </c>
-      <c r="G1581" s="3" t="s">
+      <c r="H1581" s="3" t="s">
         <v>1376</v>
       </c>
-      <c r="H1581" s="3" t="s">
+      <c r="I1581" s="3" t="s">
         <v>1377</v>
-      </c>
-      <c r="I1581" s="3" t="s">
-        <v>1378</v>
       </c>
       <c r="J1581" s="3" t="s">
         <v>489</v>
       </c>
       <c r="K1581" s="3" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="1582" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21734,10 +21739,10 @@
         <v>20</v>
       </c>
       <c r="D1582" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F1582" s="3" t="s">
         <v>1380</v>
-      </c>
-      <c r="F1582" s="3" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="1583" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21745,7 +21750,7 @@
         <v>23</v>
       </c>
       <c r="E1583" s="3" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="1584" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21769,10 +21774,10 @@
         <v>29</v>
       </c>
       <c r="D1586" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1586" s="3" t="s">
         <v>1383</v>
-      </c>
-      <c r="F1586" s="3" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="1587" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21804,10 +21809,10 @@
         <v>38</v>
       </c>
       <c r="D1590" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F1590" s="3" t="s">
         <v>1385</v>
-      </c>
-      <c r="F1590" s="3" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="1591" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21839,10 +21844,10 @@
         <v>47</v>
       </c>
       <c r="D1594" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F1594" s="3" t="s">
         <v>1387</v>
-      </c>
-      <c r="F1594" s="3" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="1595" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21874,10 +21879,10 @@
         <v>56</v>
       </c>
       <c r="D1598" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F1598" s="3" t="s">
         <v>1389</v>
-      </c>
-      <c r="F1598" s="3" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="1599" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -21909,25 +21914,25 @@
         <v>65</v>
       </c>
       <c r="F1602" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="1604" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1604" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B1604" s="8" t="s">
         <v>1392</v>
       </c>
-      <c r="B1604" s="4" t="s">
-        <v>1393</v>
-      </c>
-      <c r="C1604" s="5"/>
-      <c r="D1604" s="5"/>
-      <c r="E1604" s="5"/>
-      <c r="F1604" s="5"/>
-      <c r="G1604" s="5"/>
-      <c r="H1604" s="5"/>
-      <c r="I1604" s="5"/>
-      <c r="J1604" s="5"/>
-      <c r="K1604" s="5"/>
+      <c r="C1604" s="9"/>
+      <c r="D1604" s="9"/>
+      <c r="E1604" s="9"/>
+      <c r="F1604" s="9"/>
+      <c r="G1604" s="9"/>
+      <c r="H1604" s="9"/>
+      <c r="I1604" s="9"/>
+      <c r="J1604" s="9"/>
+      <c r="K1604" s="9"/>
     </row>
     <row r="1605" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1605" s="2" t="s">
@@ -21964,28 +21969,28 @@
     </row>
     <row r="1606" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1606" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B1606" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1606" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G1606" s="3" t="s">
         <v>1395</v>
       </c>
-      <c r="G1606" s="3" t="s">
+      <c r="H1606" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I1606" s="3" t="s">
         <v>1396</v>
-      </c>
-      <c r="H1606" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="I1606" s="3" t="s">
-        <v>1397</v>
       </c>
       <c r="J1606" s="3" t="s">
         <v>489</v>
       </c>
       <c r="K1606" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="1607" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -21993,10 +21998,10 @@
         <v>20</v>
       </c>
       <c r="D1607" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F1607" s="3" t="s">
         <v>1399</v>
-      </c>
-      <c r="F1607" s="3" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="1608" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22004,7 +22009,7 @@
         <v>23</v>
       </c>
       <c r="E1608" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="1609" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22028,10 +22033,10 @@
         <v>29</v>
       </c>
       <c r="D1611" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F1611" s="3" t="s">
         <v>1402</v>
-      </c>
-      <c r="F1611" s="3" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="1612" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22063,10 +22068,10 @@
         <v>38</v>
       </c>
       <c r="D1615" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F1615" s="3" t="s">
         <v>1404</v>
-      </c>
-      <c r="F1615" s="3" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="1616" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22098,10 +22103,10 @@
         <v>47</v>
       </c>
       <c r="D1619" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F1619" s="3" t="s">
         <v>1406</v>
-      </c>
-      <c r="F1619" s="3" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="1620" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22133,10 +22138,10 @@
         <v>56</v>
       </c>
       <c r="D1623" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F1623" s="3" t="s">
         <v>1408</v>
-      </c>
-      <c r="F1623" s="3" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="1624" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22168,25 +22173,25 @@
         <v>65</v>
       </c>
       <c r="F1627" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="1629" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1629" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1629" s="8" t="s">
         <v>1411</v>
       </c>
-      <c r="B1629" s="4" t="s">
-        <v>1412</v>
-      </c>
-      <c r="C1629" s="5"/>
-      <c r="D1629" s="5"/>
-      <c r="E1629" s="5"/>
-      <c r="F1629" s="5"/>
-      <c r="G1629" s="5"/>
-      <c r="H1629" s="5"/>
-      <c r="I1629" s="5"/>
-      <c r="J1629" s="5"/>
-      <c r="K1629" s="5"/>
+      <c r="C1629" s="9"/>
+      <c r="D1629" s="9"/>
+      <c r="E1629" s="9"/>
+      <c r="F1629" s="9"/>
+      <c r="G1629" s="9"/>
+      <c r="H1629" s="9"/>
+      <c r="I1629" s="9"/>
+      <c r="J1629" s="9"/>
+      <c r="K1629" s="9"/>
     </row>
     <row r="1630" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1630" s="2" t="s">
@@ -22223,28 +22228,28 @@
     </row>
     <row r="1631" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1631" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B1631" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1631" s="3" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G1631" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1631" s="3" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="I1631" s="3" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="J1631" s="3" t="s">
         <v>489</v>
       </c>
       <c r="K1631" s="3" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="1632" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22252,10 +22257,10 @@
         <v>20</v>
       </c>
       <c r="D1632" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F1632" s="3" t="s">
         <v>1416</v>
-      </c>
-      <c r="F1632" s="3" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="1633" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -22263,7 +22268,7 @@
         <v>23</v>
       </c>
       <c r="E1633" s="3" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="1634" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -22287,10 +22292,10 @@
         <v>29</v>
       </c>
       <c r="D1636" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1636" s="3" t="s">
         <v>1419</v>
-      </c>
-      <c r="F1636" s="3" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="1637" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -22322,10 +22327,10 @@
         <v>38</v>
       </c>
       <c r="D1640" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F1640" s="3" t="s">
         <v>1421</v>
-      </c>
-      <c r="F1640" s="3" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="1641" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -22357,10 +22362,10 @@
         <v>47</v>
       </c>
       <c r="D1644" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F1644" s="3" t="s">
         <v>1423</v>
-      </c>
-      <c r="F1644" s="3" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="1645" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -22392,10 +22397,10 @@
         <v>56</v>
       </c>
       <c r="D1648" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F1648" s="3" t="s">
         <v>1425</v>
-      </c>
-      <c r="F1648" s="3" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="1649" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22427,25 +22432,25 @@
         <v>65</v>
       </c>
       <c r="F1652" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1654" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1654" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1654" s="8" t="s">
         <v>1428</v>
       </c>
-      <c r="B1654" s="4" t="s">
-        <v>1429</v>
-      </c>
-      <c r="C1654" s="5"/>
-      <c r="D1654" s="5"/>
-      <c r="E1654" s="5"/>
-      <c r="F1654" s="5"/>
-      <c r="G1654" s="5"/>
-      <c r="H1654" s="5"/>
-      <c r="I1654" s="5"/>
-      <c r="J1654" s="5"/>
-      <c r="K1654" s="5"/>
+      <c r="C1654" s="9"/>
+      <c r="D1654" s="9"/>
+      <c r="E1654" s="9"/>
+      <c r="F1654" s="9"/>
+      <c r="G1654" s="9"/>
+      <c r="H1654" s="9"/>
+      <c r="I1654" s="9"/>
+      <c r="J1654" s="9"/>
+      <c r="K1654" s="9"/>
     </row>
     <row r="1655" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1655" s="2" t="s">
@@ -22482,28 +22487,28 @@
     </row>
     <row r="1656" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1656" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B1656" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1656" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G1656" s="3" t="s">
         <v>1431</v>
       </c>
-      <c r="G1656" s="3" t="s">
+      <c r="H1656" s="3" t="s">
         <v>1432</v>
       </c>
-      <c r="H1656" s="3" t="s">
+      <c r="I1656" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="I1656" s="3" t="s">
+      <c r="J1656" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="J1656" s="3" t="s">
+      <c r="K1656" s="3" t="s">
         <v>1435</v>
-      </c>
-      <c r="K1656" s="3" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="1657" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22511,10 +22516,10 @@
         <v>20</v>
       </c>
       <c r="D1657" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F1657" s="3" t="s">
         <v>1437</v>
-      </c>
-      <c r="F1657" s="3" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="1658" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22522,7 +22527,7 @@
         <v>23</v>
       </c>
       <c r="E1658" s="3" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1659" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22546,10 +22551,10 @@
         <v>29</v>
       </c>
       <c r="D1661" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F1661" s="3" t="s">
         <v>1440</v>
-      </c>
-      <c r="F1661" s="3" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="1662" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22581,10 +22586,10 @@
         <v>38</v>
       </c>
       <c r="D1665" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F1665" s="3" t="s">
         <v>1442</v>
-      </c>
-      <c r="F1665" s="3" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="1666" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22616,10 +22621,10 @@
         <v>47</v>
       </c>
       <c r="D1669" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F1669" s="3" t="s">
         <v>1444</v>
-      </c>
-      <c r="F1669" s="3" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="1670" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22651,10 +22656,10 @@
         <v>56</v>
       </c>
       <c r="D1673" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F1673" s="3" t="s">
         <v>1446</v>
-      </c>
-      <c r="F1673" s="3" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="1674" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22686,25 +22691,25 @@
         <v>65</v>
       </c>
       <c r="F1677" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1679" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1679" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B1679" s="8" t="s">
         <v>1449</v>
       </c>
-      <c r="B1679" s="4" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C1679" s="5"/>
-      <c r="D1679" s="5"/>
-      <c r="E1679" s="5"/>
-      <c r="F1679" s="5"/>
-      <c r="G1679" s="5"/>
-      <c r="H1679" s="5"/>
-      <c r="I1679" s="5"/>
-      <c r="J1679" s="5"/>
-      <c r="K1679" s="5"/>
+      <c r="C1679" s="9"/>
+      <c r="D1679" s="9"/>
+      <c r="E1679" s="9"/>
+      <c r="F1679" s="9"/>
+      <c r="G1679" s="9"/>
+      <c r="H1679" s="9"/>
+      <c r="I1679" s="9"/>
+      <c r="J1679" s="9"/>
+      <c r="K1679" s="9"/>
     </row>
     <row r="1680" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1680" s="2" t="s">
@@ -22741,28 +22746,28 @@
     </row>
     <row r="1681" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A1681" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B1681" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1681" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G1681" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="G1681" s="3" t="s">
+      <c r="H1681" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1681" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J1681" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K1681" s="3" t="s">
         <v>1453</v>
-      </c>
-      <c r="H1681" s="3" t="s">
-        <v>1432</v>
-      </c>
-      <c r="I1681" s="3" t="s">
-        <v>1433</v>
-      </c>
-      <c r="J1681" s="3" t="s">
-        <v>1435</v>
-      </c>
-      <c r="K1681" s="3" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="1682" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22770,10 +22775,10 @@
         <v>20</v>
       </c>
       <c r="D1682" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F1682" s="3" t="s">
         <v>1455</v>
-      </c>
-      <c r="F1682" s="3" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="1683" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22781,7 +22786,7 @@
         <v>23</v>
       </c>
       <c r="E1683" s="3" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1684" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22805,10 +22810,10 @@
         <v>29</v>
       </c>
       <c r="D1686" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F1686" s="3" t="s">
         <v>1458</v>
-      </c>
-      <c r="F1686" s="3" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="1687" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22840,10 +22845,10 @@
         <v>38</v>
       </c>
       <c r="D1690" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F1690" s="3" t="s">
         <v>1460</v>
-      </c>
-      <c r="F1690" s="3" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="1691" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22875,10 +22880,10 @@
         <v>47</v>
       </c>
       <c r="D1694" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F1694" s="3" t="s">
         <v>1462</v>
-      </c>
-      <c r="F1694" s="3" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="1695" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22910,10 +22915,10 @@
         <v>56</v>
       </c>
       <c r="D1698" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F1698" s="3" t="s">
         <v>1464</v>
-      </c>
-      <c r="F1698" s="3" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="1699" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -22945,25 +22950,25 @@
         <v>65</v>
       </c>
       <c r="F1702" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1704" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1704" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1704" s="8" t="s">
         <v>1467</v>
       </c>
-      <c r="B1704" s="4" t="s">
-        <v>1468</v>
-      </c>
-      <c r="C1704" s="5"/>
-      <c r="D1704" s="5"/>
-      <c r="E1704" s="5"/>
-      <c r="F1704" s="5"/>
-      <c r="G1704" s="5"/>
-      <c r="H1704" s="5"/>
-      <c r="I1704" s="5"/>
-      <c r="J1704" s="5"/>
-      <c r="K1704" s="5"/>
+      <c r="C1704" s="9"/>
+      <c r="D1704" s="9"/>
+      <c r="E1704" s="9"/>
+      <c r="F1704" s="9"/>
+      <c r="G1704" s="9"/>
+      <c r="H1704" s="9"/>
+      <c r="I1704" s="9"/>
+      <c r="J1704" s="9"/>
+      <c r="K1704" s="9"/>
     </row>
     <row r="1705" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1705" s="2" t="s">
@@ -23000,28 +23005,28 @@
     </row>
     <row r="1706" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1706" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1706" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1706" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G1706" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H1706" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1706" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J1706" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K1706" s="3" t="s">
         <v>1470</v>
-      </c>
-      <c r="G1706" s="3" t="s">
-        <v>1453</v>
-      </c>
-      <c r="H1706" s="3" t="s">
-        <v>1432</v>
-      </c>
-      <c r="I1706" s="3" t="s">
-        <v>1433</v>
-      </c>
-      <c r="J1706" s="3" t="s">
-        <v>1435</v>
-      </c>
-      <c r="K1706" s="3" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="1707" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23029,10 +23034,10 @@
         <v>20</v>
       </c>
       <c r="D1707" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F1707" s="3" t="s">
         <v>1472</v>
-      </c>
-      <c r="F1707" s="3" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="1708" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23040,7 +23045,7 @@
         <v>23</v>
       </c>
       <c r="E1708" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1709" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23064,10 +23069,10 @@
         <v>29</v>
       </c>
       <c r="D1711" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F1711" s="3" t="s">
         <v>1475</v>
-      </c>
-      <c r="F1711" s="3" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="1712" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23099,10 +23104,10 @@
         <v>38</v>
       </c>
       <c r="D1715" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F1715" s="3" t="s">
         <v>1477</v>
-      </c>
-      <c r="F1715" s="3" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="1716" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -23134,10 +23139,10 @@
         <v>47</v>
       </c>
       <c r="D1719" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F1719" s="3" t="s">
         <v>1479</v>
-      </c>
-      <c r="F1719" s="3" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="1720" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -23169,10 +23174,10 @@
         <v>56</v>
       </c>
       <c r="D1723" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F1723" s="3" t="s">
         <v>1481</v>
-      </c>
-      <c r="F1723" s="3" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="1724" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -23204,25 +23209,25 @@
         <v>65</v>
       </c>
       <c r="F1727" s="3" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1729" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1729" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B1729" s="8" t="s">
         <v>1484</v>
       </c>
-      <c r="B1729" s="4" t="s">
-        <v>1485</v>
-      </c>
-      <c r="C1729" s="5"/>
-      <c r="D1729" s="5"/>
-      <c r="E1729" s="5"/>
-      <c r="F1729" s="5"/>
-      <c r="G1729" s="5"/>
-      <c r="H1729" s="5"/>
-      <c r="I1729" s="5"/>
-      <c r="J1729" s="5"/>
-      <c r="K1729" s="5"/>
+      <c r="C1729" s="9"/>
+      <c r="D1729" s="9"/>
+      <c r="E1729" s="9"/>
+      <c r="F1729" s="9"/>
+      <c r="G1729" s="9"/>
+      <c r="H1729" s="9"/>
+      <c r="I1729" s="9"/>
+      <c r="J1729" s="9"/>
+      <c r="K1729" s="9"/>
     </row>
     <row r="1730" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1730" s="2" t="s">
@@ -23259,28 +23264,28 @@
     </row>
     <row r="1731" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A1731" s="1" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B1731" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1731" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G1731" s="3" t="s">
         <v>1487</v>
       </c>
-      <c r="G1731" s="3" t="s">
+      <c r="H1731" s="3" t="s">
         <v>1488</v>
       </c>
-      <c r="H1731" s="3" t="s">
+      <c r="I1731" s="3" t="s">
         <v>1489</v>
-      </c>
-      <c r="I1731" s="3" t="s">
-        <v>1490</v>
       </c>
       <c r="J1731" s="3" t="s">
         <v>489</v>
       </c>
       <c r="K1731" s="3" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1732" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23288,10 +23293,10 @@
         <v>20</v>
       </c>
       <c r="D1732" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F1732" s="3" t="s">
         <v>1492</v>
-      </c>
-      <c r="F1732" s="3" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="1733" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23299,7 +23304,7 @@
         <v>23</v>
       </c>
       <c r="E1733" s="3" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1734" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23323,10 +23328,10 @@
         <v>29</v>
       </c>
       <c r="D1736" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F1736" s="3" t="s">
         <v>1495</v>
-      </c>
-      <c r="F1736" s="3" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="1737" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23358,10 +23363,10 @@
         <v>38</v>
       </c>
       <c r="D1740" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F1740" s="3" t="s">
         <v>1497</v>
-      </c>
-      <c r="F1740" s="3" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="1741" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -23393,10 +23398,10 @@
         <v>47</v>
       </c>
       <c r="D1744" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F1744" s="3" t="s">
         <v>1499</v>
-      </c>
-      <c r="F1744" s="3" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="1745" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -23428,10 +23433,10 @@
         <v>56</v>
       </c>
       <c r="D1748" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F1748" s="3" t="s">
         <v>1501</v>
-      </c>
-      <c r="F1748" s="3" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="1749" spans="2:6" ht="16" x14ac:dyDescent="0.2">
@@ -23463,11 +23468,65 @@
         <v>65</v>
       </c>
       <c r="F1752" s="3" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="B1379:K1379"/>
+    <mergeCell ref="B1454:K1454"/>
+    <mergeCell ref="B1554:K1554"/>
+    <mergeCell ref="B304:K304"/>
+    <mergeCell ref="B1429:K1429"/>
+    <mergeCell ref="B1354:K1354"/>
+    <mergeCell ref="B1329:K1329"/>
+    <mergeCell ref="B929:K929"/>
+    <mergeCell ref="B1154:K1154"/>
+    <mergeCell ref="B554:K554"/>
+    <mergeCell ref="B203:K203"/>
+    <mergeCell ref="B529:K529"/>
+    <mergeCell ref="B279:K279"/>
+    <mergeCell ref="B879:K879"/>
+    <mergeCell ref="B1304:K1304"/>
+    <mergeCell ref="B1104:K1104"/>
+    <mergeCell ref="B729:K729"/>
+    <mergeCell ref="B1029:K1029"/>
+    <mergeCell ref="B127:K127"/>
+    <mergeCell ref="B254:K254"/>
+    <mergeCell ref="B329:K329"/>
+    <mergeCell ref="B829:K829"/>
+    <mergeCell ref="B26:K26"/>
+    <mergeCell ref="B754:K754"/>
+    <mergeCell ref="B1179:K1179"/>
+    <mergeCell ref="B1679:K1679"/>
+    <mergeCell ref="B479:K479"/>
+    <mergeCell ref="B679:K679"/>
+    <mergeCell ref="B1604:K1604"/>
+    <mergeCell ref="B404:K404"/>
+    <mergeCell ref="B1004:K1004"/>
+    <mergeCell ref="B904:K904"/>
+    <mergeCell ref="B454:K454"/>
+    <mergeCell ref="B954:K954"/>
+    <mergeCell ref="B1654:K1654"/>
+    <mergeCell ref="B804:K804"/>
+    <mergeCell ref="B704:K704"/>
+    <mergeCell ref="B604:K604"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="B77:K77"/>
+    <mergeCell ref="B152:K152"/>
+    <mergeCell ref="B228:K228"/>
+    <mergeCell ref="B1704:K1704"/>
+    <mergeCell ref="B654:K654"/>
+    <mergeCell ref="B1229:K1229"/>
+    <mergeCell ref="B1254:K1254"/>
+    <mergeCell ref="B1204:K1204"/>
+    <mergeCell ref="B629:K629"/>
+    <mergeCell ref="B1129:K1129"/>
+    <mergeCell ref="B1279:K1279"/>
+    <mergeCell ref="B1504:K1504"/>
+    <mergeCell ref="B979:K979"/>
+    <mergeCell ref="B1054:K1054"/>
+    <mergeCell ref="B779:K779"/>
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B1729:K1729"/>
     <mergeCell ref="B1629:K1629"/>
@@ -23484,60 +23543,6 @@
     <mergeCell ref="B102:K102"/>
     <mergeCell ref="B429:K429"/>
     <mergeCell ref="B504:K504"/>
-    <mergeCell ref="B52:K52"/>
-    <mergeCell ref="B77:K77"/>
-    <mergeCell ref="B152:K152"/>
-    <mergeCell ref="B228:K228"/>
-    <mergeCell ref="B1704:K1704"/>
-    <mergeCell ref="B654:K654"/>
-    <mergeCell ref="B1229:K1229"/>
-    <mergeCell ref="B1254:K1254"/>
-    <mergeCell ref="B26:K26"/>
-    <mergeCell ref="B754:K754"/>
-    <mergeCell ref="B1179:K1179"/>
-    <mergeCell ref="B1679:K1679"/>
-    <mergeCell ref="B479:K479"/>
-    <mergeCell ref="B679:K679"/>
-    <mergeCell ref="B1604:K1604"/>
-    <mergeCell ref="B404:K404"/>
-    <mergeCell ref="B1004:K1004"/>
-    <mergeCell ref="B904:K904"/>
-    <mergeCell ref="B454:K454"/>
-    <mergeCell ref="B954:K954"/>
-    <mergeCell ref="B1654:K1654"/>
-    <mergeCell ref="B804:K804"/>
-    <mergeCell ref="B704:K704"/>
-    <mergeCell ref="B604:K604"/>
-    <mergeCell ref="B1204:K1204"/>
-    <mergeCell ref="B629:K629"/>
-    <mergeCell ref="B1129:K1129"/>
-    <mergeCell ref="B1279:K1279"/>
-    <mergeCell ref="B1504:K1504"/>
-    <mergeCell ref="B979:K979"/>
-    <mergeCell ref="B1054:K1054"/>
-    <mergeCell ref="B779:K779"/>
-    <mergeCell ref="B1304:K1304"/>
-    <mergeCell ref="B1104:K1104"/>
-    <mergeCell ref="B729:K729"/>
-    <mergeCell ref="B1029:K1029"/>
-    <mergeCell ref="B127:K127"/>
-    <mergeCell ref="B254:K254"/>
-    <mergeCell ref="B329:K329"/>
-    <mergeCell ref="B829:K829"/>
-    <mergeCell ref="B1329:K1329"/>
-    <mergeCell ref="B929:K929"/>
-    <mergeCell ref="B1154:K1154"/>
-    <mergeCell ref="B554:K554"/>
-    <mergeCell ref="B203:K203"/>
-    <mergeCell ref="B529:K529"/>
-    <mergeCell ref="B279:K279"/>
-    <mergeCell ref="B879:K879"/>
-    <mergeCell ref="B1379:K1379"/>
-    <mergeCell ref="B1454:K1454"/>
-    <mergeCell ref="B1554:K1554"/>
-    <mergeCell ref="B304:K304"/>
-    <mergeCell ref="B1429:K1429"/>
-    <mergeCell ref="B1354:K1354"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <hyperlinks>
